--- a/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_hrp_monthly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_hrp_monthly.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:AO9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -890,12 +890,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -916,93 +916,97 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>9.684634074996662</v>
+        <v>2.293992173979142</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.3416882532303288</v>
+        <v>-0.7970474490116299</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.3744774130256877</v>
+        <v>-0.3839136556212107</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.08522410333287994</v>
+        <v>0.1109263358694562</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1645222726818187</v>
+        <v>0.1088831647784088</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9096847486509514</v>
+        <v>0.7181198523146833</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>0.08846498007124048</v>
+        <v>0.04358265240700065</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.3877545076850768</v>
+        <v>0.1992070464969395</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.5454410266003107</v>
+        <v>0.2722214527155001</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>0.2362358235613322</v>
+        <v>0.1135220166536654</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.8708733918691299</v>
+        <v>1.212013900201544</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="X4" s="2" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>0/6</t>
         </is>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>-0.1343200247324017</v>
+        <v>-0.7331173867362587</v>
       </c>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AF4" s="2" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="AH4" s="2" t="n">
@@ -1028,7 +1032,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1059,51 +1063,51 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>2.293992173979142</v>
+        <v>10.75132338907056</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.7970474490116299</v>
+        <v>-0.2759663856699043</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.3839136556212107</v>
+        <v>-0.3744774130256879</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.1109263358694562</v>
+        <v>0.08556675688648156</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.1088831647784088</v>
+        <v>0.1666309362679833</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.7181198523146833</v>
+        <v>0.9040045441635899</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0.04358265240700065</v>
+        <v>0.09217784818456232</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.1992070464969395</v>
+        <v>0.4032849913709411</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.2722214527155001</v>
+        <v>0.5671182213366793</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>0.1135220166536654</v>
+        <v>0.2461506221157302</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>1.212013900201544</v>
+        <v>1.314185608974349</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="X5" s="2" t="n">
@@ -1115,15 +1119,15 @@
         </is>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>-0.7331173867362587</v>
+        <v>-0.04789576606858847</v>
       </c>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="n">
@@ -1135,11 +1139,11 @@
         </is>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="AH5" s="2" t="n">
@@ -1165,7 +1169,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1183,106 +1187,100 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>10.75132338907056</v>
+        <v>4.433800608029326</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.2759663856699043</v>
+        <v>-0.6652075546283035</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.3744774130256879</v>
+        <v>-0.4206842640084347</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.08556675688648156</v>
+        <v>0.1359899187796398</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1666309362679833</v>
+        <v>0.1236369217620039</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9040045441635899</v>
+        <v>0.9379437659755752</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>0.09217784818456232</v>
+        <v>0.06244363181667811</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.4032849913709411</v>
+        <v>0.3203033865144365</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.5671182213366793</v>
+        <v>0.442578908604107</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>0.2461506221157302</v>
+        <v>0.1484334860108438</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>1.314185608974349</v>
+        <v>3.093572757198578</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="X6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>6/6</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>0/6</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="n">
+        <v>-0.559747919961465</v>
+      </c>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>5/6</t>
         </is>
       </c>
-      <c r="Z6" s="2" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="n">
-        <v>-0.04789576606858847</v>
-      </c>
-      <c r="AC6" s="2" t="n">
-        <v>0.0998339584291501</v>
-      </c>
-      <c r="AD6" s="2" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
       <c r="AF6" s="2" t="n">
-        <v>0.5</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="AH6" s="2" t="n">
@@ -1293,30 +1291,12 @@
           <t>0/6</t>
         </is>
       </c>
-      <c r="AJ6" s="2" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="AL6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>0/6</t>
-        </is>
-      </c>
-      <c r="AN6" s="2" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
+      <c r="AJ6" s="2" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" s="2" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" s="2" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1326,7 +1306,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1357,51 +1337,51 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>4.433800608029326</v>
+        <v>10.92113963248611</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.6652075546283035</v>
+        <v>-0.2655035071990015</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.4206842640084347</v>
+        <v>-0.4132656805387509</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.1359899187796398</v>
+        <v>0.09802968106171488</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1236369217620039</v>
+        <v>0.1676076722409356</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9379437659755752</v>
+        <v>0.9051405850610622</v>
       </c>
       <c r="P7" t="b">
         <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>0.06244363181667811</v>
+        <v>0.09273874452402175</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.3203033865144365</v>
+        <v>0.4040015456561222</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.442578908604107</v>
+        <v>0.5671234627107964</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>0.1484334860108438</v>
+        <v>0.2244046599831942</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>3.093572757198578</v>
+        <v>1.962006680764288</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="X7" s="2" t="n">
@@ -1413,39 +1393,39 @@
         </is>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AB7" s="2" t="n">
-        <v>-0.559747919961465</v>
+        <v>-0.03413708043011388</v>
       </c>
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AF7" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="AH7" s="2" t="n">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>1/6</t>
         </is>
       </c>
       <c r="AJ7" s="2" t="inlineStr"/>
@@ -1463,7 +1443,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1481,68 +1461,64 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>10.92113963248611</v>
+        <v>3.400852569988217</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.2655035071990015</v>
+        <v>-0.7288505228827273</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.4132656805387509</v>
+        <v>-0.2030988214540164</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.09802968106171488</v>
+        <v>0.06964593676815391</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1676076722409356</v>
+        <v>0.09296943128324564</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9051405850610622</v>
+        <v>0.8765975575120705</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>0.09273874452402175</v>
+        <v>0.05445767106851895</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.4040015456561222</v>
+        <v>0.3448160916738454</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.5671234627107964</v>
+        <v>0.4724290698896899</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>0.2244046599831942</v>
+        <v>0.2681338605445759</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>1.962006680764288</v>
+        <v>3.464272969689256</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="X8" s="2" t="n">
@@ -1554,25 +1530,23 @@
         </is>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>0/6</t>
         </is>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>-0.03413708043011388</v>
-      </c>
-      <c r="AC8" s="2" t="n">
-        <v>0.1157274595283542</v>
-      </c>
+        <v>-0.643438425948627</v>
+      </c>
+      <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="AF8" s="2" t="n">
@@ -1584,37 +1558,19 @@
         </is>
       </c>
       <c r="AH8" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>1/6</t>
-        </is>
-      </c>
-      <c r="AJ8" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>3/6</t>
-        </is>
-      </c>
-      <c r="AL8" s="2" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>1/6</t>
-        </is>
-      </c>
-      <c r="AN8" s="2" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>4/6</t>
-        </is>
-      </c>
+          <t>0/6</t>
+        </is>
+      </c>
+      <c r="AJ8" s="2" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" s="2" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" s="2" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1624,7 +1580,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1655,79 +1611,79 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>3.400852569988217</v>
+        <v>9.874857945777864</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.7288505228827273</v>
+        <v>-0.3299680007844069</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.2030988214540164</v>
+        <v>-0.4046464598524494</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.06964593676815391</v>
+        <v>0.09647584478206256</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.09296943128324564</v>
+        <v>0.1662880191109696</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.8765975575120705</v>
+        <v>0.9082646975291111</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>0.05445767106851895</v>
+        <v>0.08915256107996994</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.3448160916738454</v>
+        <v>0.3874311877779321</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.4724290698896899</v>
+        <v>0.5430280476881247</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>0.2681338605445759</v>
+        <v>0.2203221081249014</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>3.464272969689256</v>
+        <v>2.160975396310064</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="X9" s="2" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AB9" s="2" t="n">
-        <v>-0.643438425948627</v>
+        <v>-0.1189078922627897</v>
       </c>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AF9" s="2" t="n">
@@ -1752,167 +1708,6 @@
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" s="2" t="inlineStr"/>
       <c r="AO9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>hrp</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>9.874857945777864</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>-0.3299680007844069</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>-0.4046464598524494</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>0.09647584478206256</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>0.1662880191109696</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>0.9082646975291111</v>
-      </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>0.08915256107996994</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.3874311877779321</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>0.5430280476881247</v>
-      </c>
-      <c r="T10" s="3" t="n">
-        <v>0.2203221081249014</v>
-      </c>
-      <c r="U10" s="2" t="n">
-        <v>2.160975396310064</v>
-      </c>
-      <c r="V10" s="2" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="X10" s="2" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>5/6</t>
-        </is>
-      </c>
-      <c r="Z10" s="2" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="n">
-        <v>-0.1189078922627897</v>
-      </c>
-      <c r="AC10" s="2" t="n">
-        <v>0.01780349887941868</v>
-      </c>
-      <c r="AD10" s="2" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="AF10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>6/6</t>
-        </is>
-      </c>
-      <c r="AH10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>0/6</t>
-        </is>
-      </c>
-      <c r="AJ10" s="2" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="AL10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>0/6</t>
-        </is>
-      </c>
-      <c r="AN10" s="2" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>4/6</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1925,7 +1720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF10"/>
+  <dimension ref="A1:AF9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2305,12 +2100,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2320,7 +2115,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2331,68 +2126,72 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.4662306966820124</v>
+        <v>0.3842779105694654</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.6173412189194043</v>
+        <v>0.5269423347021727</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.3180206894883698</v>
+        <v>-0.08024052864543563</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.09188574888245429</v>
+        <v>0.02021149327775454</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1488918445234894</v>
+        <v>0.07840157698518678</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9418282548476454</v>
+        <v>0.4875346260387812</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.1630913374762594</v>
+        <v>0.1023585420195272</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.5804411953817679</v>
+        <v>1.081724003949144</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.3466644120689842</v>
+        <v>-0.2175717259943564</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.3180206894883698</v>
+        <v>-0.08024052864543563</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.7519602345380432</v>
+        <v>0.2557419911977641</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.02334792565864707</v>
+        <v>-0.2665010674779752</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>1.056140469786753</v>
+        <v>0.3591938168030099</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.1144491365988818</v>
+        <v>-0.0753629105092779</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.123469746284667</v>
+        <v>0.06067507418461027</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.1351727899379807</v>
+        <v>0.4952257966630542</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.01030948218372352</v>
+        <v>-0.2906254850927837</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -2408,7 +2207,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2439,62 +2238,62 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.3842779105694654</v>
+        <v>0.3327651987937918</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.5269423347021727</v>
+        <v>0.4701206952141677</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.08024052864543563</v>
+        <v>-0.3180206894883701</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.02021149327775454</v>
+        <v>0.09243141147872172</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.07840157698518678</v>
+        <v>0.1485372500354234</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.4875346260387812</v>
+        <v>0.9484764542936288</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0.1023585420195272</v>
+        <v>-0.222851313423697</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>1.081724003949144</v>
+        <v>0.4675888232512848</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.2175717259943564</v>
+        <v>0.4736892881148426</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.08024052864543563</v>
+        <v>-0.3180206894883701</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.2557419911977641</v>
+        <v>0.7149423550662293</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.2665010674779752</v>
+        <v>0.001725191635947532</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.3591938168030099</v>
+        <v>1.004148251554775</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.0753629105092779</v>
+        <v>-0.1144491365988818</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.06067507418461027</v>
+        <v>0.02120449608253261</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.4952257966630542</v>
+        <v>0.05411508118119612</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.2906254850927837</v>
+        <v>-0.03122105516390605</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -2510,7 +2309,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2528,89 +2327,79 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.3327651987937918</v>
+        <v>0.08107308521347445</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.4701206952141677</v>
+        <v>0.1924890573746585</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.3180206894883701</v>
+        <v>-0.4206842640084347</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.09243141147872172</v>
+        <v>0.2178191233697231</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1485372500354234</v>
+        <v>0.1398884103485653</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9484764542936288</v>
+        <v>0.9950138504155125</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.222851313423697</v>
+        <v>-0.3041304927991617</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.4675888232512848</v>
+        <v>0.3140989991354248</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.4736892881148426</v>
+        <v>0.6464550485020032</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.3180206894883701</v>
+        <v>-0.4206842640084347</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.7149423550662293</v>
+        <v>0.5535572029332516</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.001725191635947532</v>
+        <v>-0.09254245063787137</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>1.004148251554775</v>
+        <v>0.7774801611935339</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.1144491365988818</v>
+        <v>-0.1175306843923516</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.02120449608253261</v>
+        <v>-0.1716495176997583</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.05411508118119612</v>
+        <v>-0.05613101489490768</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.03122105516390605</v>
-      </c>
-      <c r="AB6" s="2" t="n">
-        <v>-0.09102626086757326</v>
-      </c>
-      <c r="AC6" s="2" t="n">
-        <v>-0.07140561285054503</v>
-      </c>
-      <c r="AD6" s="2" t="n">
-        <v>-0.02112940621713066</v>
-      </c>
+        <v>-0.1223882812422197</v>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
       <c r="AE6" s="2" t="inlineStr"/>
       <c r="AF6" s="2" t="inlineStr"/>
     </row>
@@ -2622,7 +2411,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2653,62 +2442,62 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.08107308521347445</v>
+        <v>0.3220281375575083</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.1924890573746585</v>
+        <v>0.4582770666864058</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.4206842640084347</v>
+        <v>-0.3514343814258261</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.2178191233697231</v>
+        <v>0.1146575544984008</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1398884103485653</v>
+        <v>0.1517987871375321</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9950138504155125</v>
+        <v>0.9523545706371191</v>
       </c>
       <c r="P7" t="b">
         <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.3041304927991617</v>
+        <v>-0.2560887104785098</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.3140989991354248</v>
+        <v>0.4048224141018315</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.6464550485020032</v>
+        <v>0.5443381826975319</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.4206842640084347</v>
+        <v>-0.3514343814258261</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.5535572029332516</v>
+        <v>0.7771314351310399</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.09254245063787137</v>
+        <v>0.03805082553352523</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.7774801611935339</v>
+        <v>1.091493833433324</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.1175306843923516</v>
+        <v>-0.1175306843923517</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.1716495176997583</v>
+        <v>0.01297743911921323</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>-0.05613101489490768</v>
+        <v>0.009032277723037385</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.1223882812422197</v>
+        <v>0.003909846576046538</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -2724,7 +2513,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2742,91 +2531,85 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.3220281375575083</v>
+        <v>0.5514382080702624</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.4582770666864058</v>
+        <v>0.7113302621454229</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.3514343814258261</v>
+        <v>-0.0845172612821613</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.1146575544984008</v>
+        <v>0.03285844017798271</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1517987871375321</v>
+        <v>0.08600622972498906</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9523545706371191</v>
+        <v>0.8288088642659279</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.2560887104785098</v>
+        <v>0.03608271871848556</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.4048224141018315</v>
+        <v>0.9565669275640758</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.5443381826975319</v>
+        <v>-0.07669686608717131</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.3514343814258261</v>
+        <v>-0.0845172612821613</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.7771314351310399</v>
+        <v>0.4974076683657191</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.03805082553352523</v>
+        <v>-0.1253402896490599</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>1.091493833433324</v>
+        <v>0.6986172199199271</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.1175306843923517</v>
+        <v>-0.07930571287241328</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.01297743911921323</v>
+        <v>0.1887582860878043</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.009032277723037385</v>
+        <v>0.4053300713455428</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>0.003909846576046538</v>
-      </c>
-      <c r="AB8" s="2" t="n">
-        <v>-0.09834916118645276</v>
-      </c>
-      <c r="AC8" s="2" t="n">
-        <v>-0.111120098484597</v>
-      </c>
-      <c r="AD8" s="2" t="n">
-        <v>0.01436744972675363</v>
-      </c>
-      <c r="AE8" s="2" t="inlineStr"/>
-      <c r="AF8" s="2" t="inlineStr"/>
+        <v>-0.1541074155272151</v>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
+      <c r="AE8" s="2" t="n">
+        <v>-0.001279829547892186</v>
+      </c>
+      <c r="AF8" s="2" t="n">
+        <v>0.009113158068361216</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2836,7 +2619,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2867,62 +2650,62 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.5514382080702624</v>
+        <v>0.3937688239936334</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.7113302621454229</v>
+        <v>0.5374113867557402</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.0845172612821613</v>
+        <v>-0.3272689968646514</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.03285844017798271</v>
+        <v>0.09602380804475916</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.08600622972498906</v>
+        <v>0.1495505253008701</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.8288088642659279</v>
+        <v>0.9440443213296399</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>0.03608271871848556</v>
+        <v>-0.2111603173563172</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.9565669275640758</v>
+        <v>0.4896664198007279</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>-0.07669686608717131</v>
+        <v>0.4488390885830068</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.0845172612821613</v>
+        <v>-0.3272689968646514</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.4974076683657191</v>
+        <v>0.7668594198032961</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.1253402896490599</v>
+        <v>0.03205077748976803</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.6986172199199271</v>
+        <v>1.077066619605235</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.07930571287241328</v>
+        <v>-0.1144491365988818</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.1887582860878043</v>
+        <v>0.06794729548020095</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.4053300713455428</v>
+        <v>0.06997260687933049</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.1541074155272151</v>
+        <v>-0.001892862850981114</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
@@ -2931,122 +2714,6 @@
         <v>-0.001279829547892186</v>
       </c>
       <c r="AF9" s="2" t="n">
-        <v>0.009113158068361216</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>hrp</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>0.3937688239936334</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>0.5374113867557402</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>-0.3272689968646514</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>0.09602380804475916</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>0.1495505253008701</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>0.9440443213296399</v>
-      </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>-0.2111603173563172</v>
-      </c>
-      <c r="R10" s="2" t="n">
-        <v>0.4896664198007279</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>0.4488390885830068</v>
-      </c>
-      <c r="T10" s="2" t="n">
-        <v>-0.3272689968646514</v>
-      </c>
-      <c r="U10" s="2" t="n">
-        <v>0.7668594198032961</v>
-      </c>
-      <c r="V10" s="2" t="n">
-        <v>0.03205077748976803</v>
-      </c>
-      <c r="W10" s="3" t="n">
-        <v>1.077066619605235</v>
-      </c>
-      <c r="X10" s="2" t="n">
-        <v>-0.1144491365988818</v>
-      </c>
-      <c r="Y10" s="2" t="n">
-        <v>0.06794729548020095</v>
-      </c>
-      <c r="Z10" s="2" t="n">
-        <v>0.06997260687933049</v>
-      </c>
-      <c r="AA10" s="2" t="n">
-        <v>-0.001892862850981114</v>
-      </c>
-      <c r="AB10" s="2" t="n">
-        <v>-0.04942051264671765</v>
-      </c>
-      <c r="AC10" s="2" t="n">
-        <v>-0.05743635122033919</v>
-      </c>
-      <c r="AD10" s="2" t="n">
-        <v>0.00850429420230614</v>
-      </c>
-      <c r="AE10" s="2" t="n">
-        <v>-0.001279829547892186</v>
-      </c>
-      <c r="AF10" s="2" t="n">
         <v>-0.06347578376244911</v>
       </c>
     </row>
@@ -3061,7 +2728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF10"/>
+  <dimension ref="A1:AF9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3441,12 +3108,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3456,7 +3123,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3467,74 +3134,82 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.4214855010465173</v>
+        <v>0.1906243837459807</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.3487784252242632</v>
+        <v>0.1297255442705785</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.3744774130256878</v>
+        <v>-0.124381038500744</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1200249121443981</v>
+        <v>0.02820039558833212</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.200292846208758</v>
+        <v>0.07209321945407876</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9244186046511628</v>
+        <v>0.3292151162790697</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.3743492138682257</v>
+        <v>0.02220992715952153</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.2601459135591284</v>
+        <v>1.058870045499055</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.7434803069533858</v>
+        <v>-0.04411026616389797</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.3744774130256878</v>
+        <v>0</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>1.272011052419783</v>
+        <v>0.1647552543873674</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.07033511810930126</v>
+        <v>-0.4512885615387436</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>1.132982746142185</v>
+        <v>0.1467478291183522</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.1172230559518105</v>
+        <v>-0.124381038500744</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.1323023943399293</v>
+        <v>-0.05159297123850193</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.1496653620696891</v>
+        <v>0.8783630933879494</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.01510262751458558</v>
+        <v>-0.4950885523145134</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="inlineStr"/>
-      <c r="AE4" s="2" t="inlineStr"/>
-      <c r="AF4" s="2" t="inlineStr"/>
+      <c r="AE4" s="2" t="n">
+        <v>0.1213750437267103</v>
+      </c>
+      <c r="AF4" s="2" t="n">
+        <v>-0.0871167904264869</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3544,7 +3219,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3575,62 +3250,62 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.1906243837459807</v>
+        <v>0.3619902625519242</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.1297255442705785</v>
+        <v>0.2923262883392925</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.124381038500744</v>
+        <v>-0.3744774130256878</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.02820039558833212</v>
+        <v>0.1204024944056784</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.07209321945407876</v>
+        <v>0.2016293480415229</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.3292151162790697</v>
+        <v>0.9280523255813954</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0.02220992715952153</v>
+        <v>-0.3743492138682257</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>1.058870045499055</v>
+        <v>0.2601459135591284</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.04411026616389797</v>
+        <v>0.7434803069533858</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>0</v>
+        <v>-0.3744774130256878</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.1647552543873674</v>
+        <v>1.176917687537377</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.4512885615387436</v>
+        <v>0.02553702268436098</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.1467478291183522</v>
+        <v>1.048282899014745</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.124381038500744</v>
+        <v>-0.1243810385007439</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.05159297123850193</v>
+        <v>0.0849107037812451</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.8783630933879494</v>
+        <v>0.1496653620696891</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.4950885523145134</v>
+        <v>-0.05632478843397448</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -3639,7 +3314,7 @@
         <v>0.1213750437267103</v>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>-0.0871167904264869</v>
+        <v>0.01477161720148734</v>
       </c>
     </row>
     <row r="6">
@@ -3650,7 +3325,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3668,95 +3343,81 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.3619902625519242</v>
+        <v>0.288558478756942</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.2923262883392925</v>
+        <v>0.2226504417439612</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.3744774130256878</v>
+        <v>-0.2686838800141741</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.1204024944056784</v>
+        <v>0.1127733585915732</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.2016293480415229</v>
+        <v>0.1149667393730911</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9280523255813954</v>
+        <v>0.9404069767441861</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.3743492138682257</v>
+        <v>-0.2419911218891416</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.2601459135591284</v>
+        <v>0.5267331415000467</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.7434803069533858</v>
+        <v>0.4806090861605632</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.3744774130256878</v>
+        <v>-0.2421992389158157</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>1.176917687537377</v>
+        <v>0.6999253121788516</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.02553702268436098</v>
+        <v>-0.1991721352543104</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>1.048282899014745</v>
+        <v>0.6234248521490975</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.1243810385007439</v>
+        <v>-0.1243810385007441</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.0849107037812451</v>
+        <v>0.02641768042610249</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.1496653620696891</v>
+        <v>0.3928801347686841</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.05632478843397448</v>
-      </c>
-      <c r="AB6" s="2" t="n">
-        <v>-0.04185427037475364</v>
-      </c>
-      <c r="AC6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="2" t="n">
-        <v>-0.04185427037475353</v>
-      </c>
-      <c r="AE6" s="2" t="n">
-        <v>0.1213750437267103</v>
-      </c>
-      <c r="AF6" s="2" t="n">
-        <v>0.01477161720148734</v>
-      </c>
+        <v>-0.2630969063274349</v>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3766,7 +3427,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3797,62 +3458,62 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.288558478756942</v>
+        <v>0.3192077111603842</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.2226504417439612</v>
+        <v>0.2517320070395712</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.2686838800141741</v>
+        <v>-0.4132656805387505</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.1127733585915732</v>
+        <v>0.1480984800720592</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1149667393730911</v>
+        <v>0.2046700509379647</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9404069767441861</v>
+        <v>0.9375</v>
       </c>
       <c r="P7" t="b">
         <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.2419911218891416</v>
+        <v>-0.4132656805387506</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.5267331415000467</v>
+        <v>0.1817628482261089</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.4806090861605632</v>
+        <v>0.8207707766908965</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.2421992389158157</v>
+        <v>-0.4132656805387505</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.6999253121788516</v>
+        <v>1.24839022945122</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.1991721352543104</v>
+        <v>0.05920744497805952</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.6234248521490975</v>
+        <v>1.111943632667383</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.1243810385007441</v>
+        <v>-0.1243810385007439</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.02641768042610249</v>
+        <v>0.05083171715707779</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.3928801347686841</v>
+        <v>0.07815436146524224</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.2630969063274349</v>
+        <v>-0.02534205238573839</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -3868,7 +3529,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3886,89 +3547,79 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.3192077111603842</v>
+        <v>0.1542976500171809</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.2517320070395712</v>
+        <v>0.09525687422350471</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.4132656805387505</v>
+        <v>-0.1975522224118726</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.1480984800720592</v>
+        <v>0.09525881742785987</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.2046700509379647</v>
+        <v>0.1047304945378492</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9375</v>
+        <v>0.9534883720930233</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.4132656805387506</v>
+        <v>-0.1428215242055786</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.1817628482261089</v>
+        <v>0.7264742207734993</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.8207707766908965</v>
+        <v>0.2836522335887476</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.4132656805387505</v>
+        <v>-0.1529693814334363</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>1.24839022945122</v>
+        <v>0.3466246325742062</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.05920744497805952</v>
+        <v>-0.3656106410133336</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>1.111943632667383</v>
+        <v>0.3087392419644215</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.1243810385007439</v>
+        <v>-0.1383494719981027</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.05083171715707779</v>
+        <v>-0.08052949401652998</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.07815436146524224</v>
+        <v>0.5751093494590109</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.02534205238573839</v>
-      </c>
-      <c r="AB8" s="2" t="n">
-        <v>-0.0719513423181839</v>
-      </c>
-      <c r="AC8" s="2" t="n">
-        <v>-0.06220157879307497</v>
-      </c>
-      <c r="AD8" s="2" t="n">
-        <v>-0.01039643840790572</v>
-      </c>
+        <v>-0.4162497312968952</v>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
     </row>
@@ -3980,7 +3631,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4011,180 +3662,68 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.1542976500171809</v>
+        <v>0.3403836730152192</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.09525687422350471</v>
+        <v>0.2718248468625213</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.1975522224118726</v>
+        <v>-0.4046464598524491</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.09525881742785987</v>
+        <v>0.1428854981937125</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1047304945378492</v>
+        <v>0.2036074392398008</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9534883720930233</v>
+        <v>0.936046511627907</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.1428215242055786</v>
+        <v>-0.4046464598524491</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.7264742207734993</v>
+        <v>0.1991231328555914</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.2836522335887476</v>
+        <v>0.8036524801801787</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.1529693814334363</v>
+        <v>-0.4046464598524491</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.3466246325742062</v>
+        <v>1.251407915846141</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.3656106410133336</v>
+        <v>0.06062906470146912</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.3087392419644215</v>
+        <v>1.114631491874431</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.1383494719981027</v>
+        <v>-0.1243810385007439</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.08052949401652998</v>
+        <v>0.06769969948474008</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.5751093494590109</v>
+        <v>0.09399262090760852</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.4162497312968952</v>
+        <v>-0.02403391112552</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
       <c r="AE9" s="2" t="inlineStr"/>
       <c r="AF9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>hrp</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>0.3403836730152192</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>0.2718248468625213</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>-0.4046464598524491</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>0.1428854981937125</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>0.2036074392398008</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>0.936046511627907</v>
-      </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>-0.4046464598524491</v>
-      </c>
-      <c r="R10" s="2" t="n">
-        <v>0.1991231328555914</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>0.8036524801801787</v>
-      </c>
-      <c r="T10" s="2" t="n">
-        <v>-0.4046464598524491</v>
-      </c>
-      <c r="U10" s="2" t="n">
-        <v>1.251407915846141</v>
-      </c>
-      <c r="V10" s="2" t="n">
-        <v>0.06062906470146912</v>
-      </c>
-      <c r="W10" s="3" t="n">
-        <v>1.114631491874431</v>
-      </c>
-      <c r="X10" s="2" t="n">
-        <v>-0.1243810385007439</v>
-      </c>
-      <c r="Y10" s="2" t="n">
-        <v>0.06769969948474008</v>
-      </c>
-      <c r="Z10" s="2" t="n">
-        <v>0.09399262090760852</v>
-      </c>
-      <c r="AA10" s="2" t="n">
-        <v>-0.02403391112552</v>
-      </c>
-      <c r="AB10" s="2" t="n">
-        <v>-0.05705427735392998</v>
-      </c>
-      <c r="AC10" s="2" t="n">
-        <v>-0.04842517048774575</v>
-      </c>
-      <c r="AD10" s="2" t="n">
-        <v>-0.009068237829080728</v>
-      </c>
-      <c r="AE10" s="2" t="inlineStr"/>
-      <c r="AF10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4197,7 +3736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF10"/>
+  <dimension ref="A1:AF9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4577,12 +4116,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -4592,7 +4131,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -4603,68 +4142,72 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.001802582320870938</v>
+        <v>0.0189637709832835</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.0211130349041182</v>
+        <v>-0.004344397865602034</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.143729669862375</v>
+        <v>-0.1452798889626855</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.04690988384817812</v>
+        <v>0.04520489920804412</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.153917301860116</v>
+        <v>0.165114162844639</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9862068965517241</v>
+        <v>0.9448275862068966</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.1360620360985055</v>
+        <v>-0.1425767900867722</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.07379760643682176</v>
+        <v>0.06570035000010499</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.696194308369228</v>
+        <v>0.7295286224594077</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.143729669862375</v>
+        <v>-0.1452798889626855</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.1595769883716971</v>
+        <v>0.1884023656024003</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.08838783097671599</v>
+        <v>-0.06572649419295029</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.586665176447165</v>
+        <v>0.6926381315189625</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.02128572850164578</v>
+        <v>-0.02330447460112961</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.01684180453820483</v>
+        <v>0</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.007598061159233005</v>
+        <v>0</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.02425557039016124</v>
+        <v>0</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -4680,7 +4223,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4711,7 +4254,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
@@ -4782,7 +4325,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4800,40 +4343,36 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.0189637709832835</v>
+        <v>0.02101828569239994</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.004344397865602034</v>
+        <v>-0.002336878915418672</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.1452798889626855</v>
+        <v>-0.05636256056298983</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.04520489920804412</v>
+        <v>0.02273032266102984</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.165114162844639</v>
+        <v>0.08866814164939027</v>
       </c>
       <c r="O6" s="2" t="n">
         <v>0.9448275862068966</v>
@@ -4842,47 +4381,41 @@
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.1425767900867722</v>
+        <v>-0.02352288142809378</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.06570035000010499</v>
+        <v>0.2136737086164107</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.7295286224594077</v>
+        <v>0.1203605108101347</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.1452798889626855</v>
+        <v>-0.05636256056298983</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.1884023656024003</v>
+        <v>0.04561414320249013</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.06572649419295029</v>
+        <v>-0.1779807752267135</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.6926381315189625</v>
+        <v>0.167694788850404</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.02330447460112961</v>
+        <v>-0.01299965782681711</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0</v>
+        <v>0.002016278466047794</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0</v>
+        <v>0.1388508116904448</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="2" t="n">
-        <v>0.01713030986869213</v>
-      </c>
-      <c r="AC6" s="2" t="n">
-        <v>-0.007540765958294449</v>
-      </c>
-      <c r="AD6" s="2" t="n">
-        <v>0.02485852816998424</v>
-      </c>
+        <v>-0.1201514121250767</v>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
       <c r="AE6" s="2" t="inlineStr"/>
       <c r="AF6" s="2" t="inlineStr"/>
     </row>
@@ -4894,7 +4427,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4925,62 +4458,62 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.02101828569239994</v>
+        <v>0.009997036596348874</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.002336878915418672</v>
+        <v>-0.01310602372457392</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.05636256056298983</v>
+        <v>-0.1437296698623749</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.02273032266102984</v>
+        <v>0.04713651623559876</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.08866814164939027</v>
+        <v>0.1582645991808558</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9448275862068966</v>
+        <v>0.9724137931034482</v>
       </c>
       <c r="P7" t="b">
         <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.02352288142809378</v>
+        <v>-0.1418475533411728</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.2136737086164107</v>
+        <v>0.06660672604175288</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.1203605108101347</v>
+        <v>0.725797306316436</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.05636256056298983</v>
+        <v>-0.1437296698623749</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.04561414320249013</v>
+        <v>0.1769436077805531</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.1779807752267135</v>
+        <v>-0.0747349025841475</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.167694788850404</v>
+        <v>0.6505114173353299</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.01299965782681711</v>
+        <v>-0.02128572850164578</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.002016278466047794</v>
+        <v>-0.00879985593431043</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.1388508116904448</v>
+        <v>0.0008504980238090987</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.1201514121250767</v>
+        <v>-0.009642153325770897</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -4996,7 +4529,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -5014,89 +4547,79 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.009997036596348874</v>
+        <v>0.03628551780779454</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.01310602372457392</v>
+        <v>0.01258112466591599</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.1437296698623749</v>
+        <v>-0.05636256056298983</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.04713651623559876</v>
+        <v>0.02181766856855238</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1582645991808558</v>
+        <v>0.09381119840717209</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9724137931034482</v>
+        <v>0.9172413793103448</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.1418475533411728</v>
+        <v>-0.02352288142809378</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.06660672604175288</v>
+        <v>0.2136737086164107</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.725797306316436</v>
+        <v>0.1203605108101347</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.1437296698623749</v>
+        <v>-0.05636256056298983</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.1769436077805531</v>
+        <v>0.06124915586691659</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.0747349025841475</v>
+        <v>-0.1656891654839755</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.6505114173353299</v>
+        <v>0.2251749904579453</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.02128572850164578</v>
+        <v>-0.01241008337108096</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.00879985593431043</v>
+        <v>0.01699937457815182</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.0008504980238090987</v>
+        <v>0.1388508116904448</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.009642153325770897</v>
-      </c>
-      <c r="AB8" s="2" t="n">
-        <v>0.008179709675427249</v>
-      </c>
-      <c r="AC8" s="2" t="n">
-        <v>-0.006696681341030852</v>
-      </c>
-      <c r="AD8" s="2" t="n">
-        <v>0.01497668510414529</v>
-      </c>
+        <v>-0.1069950829919712</v>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
     </row>
@@ -5108,7 +4631,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -5139,180 +4662,68 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.03628551780779454</v>
+        <v>0.0133351018917065</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.01258112466591599</v>
+        <v>-0.009844314617481698</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.05636256056298983</v>
+        <v>-0.1437296698623749</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.02181766856855238</v>
+        <v>0.04678736816659274</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.09381119840717209</v>
+        <v>0.1585358318065773</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9172413793103448</v>
+        <v>0.9586206896551724</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.02352288142809378</v>
+        <v>-0.1418475533411728</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.2136737086164107</v>
+        <v>0.06660672604175288</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.1203605108101347</v>
+        <v>0.725797306316436</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.05636256056298983</v>
+        <v>-0.1437296698623749</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.06124915586691659</v>
+        <v>0.1808334356408061</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.1656891654839755</v>
+        <v>-0.07167687845261317</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.2251749904579453</v>
+        <v>0.6648118911772664</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.01241008337108096</v>
+        <v>-0.02128572850164578</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.01699937457815182</v>
+        <v>-0.005523914835701582</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.1388508116904448</v>
+        <v>0.0008504980238090987</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.1069950829919712</v>
+        <v>-0.006368996040964192</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
       <c r="AE9" s="2" t="inlineStr"/>
       <c r="AF9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>hrp</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>0.0133351018917065</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>-0.009844314617481698</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>-0.1437296698623749</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>0.04678736816659274</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>0.1585358318065773</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>0.9586206896551724</v>
-      </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>-0.1418475533411728</v>
-      </c>
-      <c r="R10" s="2" t="n">
-        <v>0.06660672604175288</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>0.725797306316436</v>
-      </c>
-      <c r="T10" s="2" t="n">
-        <v>-0.1437296698623749</v>
-      </c>
-      <c r="U10" s="2" t="n">
-        <v>0.1808334356408061</v>
-      </c>
-      <c r="V10" s="2" t="n">
-        <v>-0.07167687845261317</v>
-      </c>
-      <c r="W10" s="3" t="n">
-        <v>0.6648118911772664</v>
-      </c>
-      <c r="X10" s="2" t="n">
-        <v>-0.02128572850164578</v>
-      </c>
-      <c r="Y10" s="2" t="n">
-        <v>-0.005523914835701582</v>
-      </c>
-      <c r="Z10" s="2" t="n">
-        <v>0.0008504980238090987</v>
-      </c>
-      <c r="AA10" s="2" t="n">
-        <v>-0.006368996040964192</v>
-      </c>
-      <c r="AB10" s="2" t="n">
-        <v>0.0115117686601669</v>
-      </c>
-      <c r="AC10" s="2" t="n">
-        <v>-0.006696681341030852</v>
-      </c>
-      <c r="AD10" s="2" t="n">
-        <v>0.01833120826152101</v>
-      </c>
-      <c r="AE10" s="2" t="inlineStr"/>
-      <c r="AF10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5325,7 +4736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF10"/>
+  <dimension ref="A1:AF9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5705,12 +5116,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -5720,7 +5131,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -5731,68 +5142,72 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.0001327025339010746</v>
+        <v>-0.2274421683855108</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.08898835292102503</v>
+        <v>-0.2962842022266335</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.2893340076613283</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1193940004707371</v>
+        <v>0.2150465200281015</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.4109397789559724</v>
+        <v>0.376471579977516</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9918032786885246</v>
+        <v>1</v>
       </c>
       <c r="P4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.2893340076613283</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.00124772041103749</v>
+        <v>-0.00807433626786469</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.9969484920130616</v>
+        <v>1.019747133566668</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.2893340076613283</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.4073175209111213</v>
+        <v>0.09730631722911864</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.09012362424657316</v>
+        <v>-0.2905559120976615</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.7450300267984358</v>
+        <v>0.17798431054648</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.0790522597965585</v>
+        <v>-0.05119781779615939</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.001088151244975855</v>
+        <v>-0.2267041269410339</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.009397938796973815</v>
+        <v>0</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.008232419774803046</v>
+        <v>-0.2267041269410338</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -5808,7 +5223,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -5839,23 +5254,23 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0.2274421683855108</v>
+        <v>-0.01329447775510906</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.2962842022266335</v>
+        <v>-0.1012190475075795</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>-0.295950620638614</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.2150465200281015</v>
+        <v>0.1283082103708132</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.376471579977516</v>
+        <v>0.4246186257165711</v>
       </c>
       <c r="O5" s="2" t="n">
         <v>1</v>
@@ -5876,25 +5291,25 @@
         <v>-0.295950620638614</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.09730631722911864</v>
+        <v>0.4014720432534016</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.2905559120976615</v>
+        <v>-0.09390291495156644</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.17798431054648</v>
+        <v>0.7343379839758271</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.05119781779615939</v>
+        <v>-0.0790522597965585</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.2267041269410339</v>
+        <v>-0.01235185632392233</v>
       </c>
       <c r="Z5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.2267041269410338</v>
+        <v>-0.01235185632392222</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -5910,7 +5325,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -5928,91 +5343,85 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0.01329447775510906</v>
+        <v>0.02943958852926998</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.1012190475075795</v>
+        <v>-0.06229298098312785</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.07538615706116925</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.1283082103708132</v>
+        <v>0.02800300401528761</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.4246186257165711</v>
+        <v>0.1136941935630939</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1</v>
+        <v>0.4180327868852459</v>
       </c>
       <c r="P6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.295950620638614</v>
+        <v>0.0007182735616988456</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.00807433626786469</v>
+        <v>0.4098984628208118</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>1.019747133566668</v>
+        <v>-0.002474931135736743</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.295950620638614</v>
+        <v>0</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.4014720432534016</v>
+        <v>0.02870070001354907</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.09390291495156644</v>
+        <v>-0.3349116665176135</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.7343379839758271</v>
+        <v>0.0524968414135423</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.0790522597965585</v>
+        <v>-0.07538615706116913</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.01235185632392233</v>
+        <v>0.0304230347514538</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0</v>
+        <v>0.4213751235309786</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.01235185632392222</v>
-      </c>
-      <c r="AB6" s="2" t="n">
-        <v>-0.01342539870458337</v>
-      </c>
-      <c r="AC6" s="2" t="n">
-        <v>-0.009310439853061792</v>
-      </c>
-      <c r="AD6" s="2" t="n">
-        <v>-0.004153630982960621</v>
-      </c>
-      <c r="AE6" s="2" t="inlineStr"/>
-      <c r="AF6" s="2" t="inlineStr"/>
+        <v>-0.2750520128763206</v>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
+      <c r="AE6" s="2" t="n">
+        <v>0.02027751002917078</v>
+      </c>
+      <c r="AF6" s="2" t="n">
+        <v>-0.0192674312508917</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6022,7 +5431,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -6053,62 +5462,62 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.02943958852926998</v>
+        <v>-0.007407262005415527</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.06229298098312785</v>
+        <v>-0.0958564370227416</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.07538615706116925</v>
+        <v>-0.2893340076613283</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.02800300401528761</v>
+        <v>0.1198547310511575</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1136941935630939</v>
+        <v>0.4118484759031685</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.4180327868852459</v>
+        <v>1</v>
       </c>
       <c r="P7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>0.0007182735616988456</v>
+        <v>-0.2893340076613283</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.4098984628208118</v>
+        <v>0.00124772041103749</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.002474931135736743</v>
+        <v>0.9969484920130616</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>0</v>
+        <v>-0.2893340076613283</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.02870070001354907</v>
+        <v>0.3967078046441248</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.3349116665176135</v>
+        <v>-0.09698314957852316</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.0524968414135423</v>
+        <v>0.7256236502275419</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.07538615706116913</v>
+        <v>-0.07538615706116902</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.0304230347514538</v>
+        <v>-0.006459016387872718</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.4213751235309786</v>
+        <v>0.009397938796973815</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.2750520128763206</v>
+        <v>-0.01570931995734504</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -6117,7 +5526,7 @@
         <v>0.02027751002917078</v>
       </c>
       <c r="AF7" s="2" t="n">
-        <v>-0.0192674312508917</v>
+        <v>-0.004450505083797629</v>
       </c>
     </row>
     <row r="8">
@@ -6128,7 +5537,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -6146,40 +5555,36 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0.007407262005415527</v>
+        <v>-0.03877647638945059</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.0958564370227416</v>
+        <v>-0.1244303648536882</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.2893340076613283</v>
+        <v>-0.1195800593377413</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.1198547310511575</v>
+        <v>0.07321180804657658</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.4118484759031685</v>
+        <v>0.1191644851747677</v>
       </c>
       <c r="O8" s="2" t="n">
         <v>1</v>
@@ -6188,53 +5593,43 @@
         <v>0</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.2893340076613283</v>
+        <v>-0.07487432247921966</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.00124772041103749</v>
+        <v>0.3033970749932469</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.9969484920130616</v>
+        <v>0.2579919432544974</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.2893340076613283</v>
+        <v>-0.1195800593377413</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.3967078046441248</v>
+        <v>0.03901939700399049</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.09698314957852316</v>
+        <v>-0.3282402945772698</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.7256236502275419</v>
+        <v>0.07137091066083846</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.07538615706116902</v>
+        <v>-0.005374568503844879</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.006459016387872718</v>
+        <v>-0.03785819847056893</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.009397938796973815</v>
+        <v>0.3140068078178315</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.01570931995734504</v>
-      </c>
-      <c r="AB8" s="2" t="n">
-        <v>-0.007538964099677581</v>
-      </c>
-      <c r="AC8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" s="2" t="n">
-        <v>-0.007538964099677803</v>
-      </c>
-      <c r="AE8" s="2" t="n">
-        <v>0.02027751002917078</v>
-      </c>
-      <c r="AF8" s="2" t="n">
-        <v>-0.004450505083797629</v>
-      </c>
+        <v>-0.2677802003725855</v>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
+      <c r="AE8" s="2" t="inlineStr"/>
+      <c r="AF8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6244,7 +5639,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -6275,23 +5670,23 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0.03877647638945059</v>
+        <v>-0.008142625018193739</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.1244303648536882</v>
+        <v>-0.09652627240336131</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.1195800593377413</v>
+        <v>-0.2918967743785572</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.07321180804657658</v>
+        <v>0.1221338087310294</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1191644851747677</v>
+        <v>0.4111036892321253</v>
       </c>
       <c r="O9" s="2" t="n">
         <v>1</v>
@@ -6300,155 +5695,43 @@
         <v>0</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.07487432247921966</v>
+        <v>-0.2918967743785572</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.3033970749932469</v>
+        <v>-0.002362927011567595</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.2579919432544974</v>
+        <v>1.005778931389249</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.1195800593377413</v>
+        <v>-0.2918967743785572</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.03901939700399049</v>
+        <v>0.40072427167852</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.3282402945772698</v>
+        <v>-0.09438637350326862</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.07137091066083846</v>
+        <v>0.7329702248005602</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.005374568503844879</v>
+        <v>-0.0790522597965585</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.03785819847056893</v>
+        <v>-0.007195081909069034</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.3140068078178315</v>
+        <v>0.005757900480977352</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.2677802003725855</v>
+        <v>-0.01287882738365964</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
       <c r="AE9" s="2" t="inlineStr"/>
       <c r="AF9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>hrp</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>-0.008142625018193739</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>-0.09652627240336131</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>-0.2918967743785572</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>0.1221338087310294</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>0.4111036892321253</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P10" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>-0.2918967743785572</v>
-      </c>
-      <c r="R10" s="2" t="n">
-        <v>-0.002362927011567595</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>1.005778931389249</v>
-      </c>
-      <c r="T10" s="2" t="n">
-        <v>-0.2918967743785572</v>
-      </c>
-      <c r="U10" s="2" t="n">
-        <v>0.40072427167852</v>
-      </c>
-      <c r="V10" s="2" t="n">
-        <v>-0.09438637350326862</v>
-      </c>
-      <c r="W10" s="3" t="n">
-        <v>0.7329702248005602</v>
-      </c>
-      <c r="X10" s="2" t="n">
-        <v>-0.0790522597965585</v>
-      </c>
-      <c r="Y10" s="2" t="n">
-        <v>-0.007195081909069034</v>
-      </c>
-      <c r="Z10" s="2" t="n">
-        <v>0.005757900480977352</v>
-      </c>
-      <c r="AA10" s="2" t="n">
-        <v>-0.01287882738365964</v>
-      </c>
-      <c r="AB10" s="2" t="n">
-        <v>-0.008274229540868649</v>
-      </c>
-      <c r="AC10" s="2" t="n">
-        <v>-0.003606147958192363</v>
-      </c>
-      <c r="AD10" s="2" t="n">
-        <v>-0.004684976300396437</v>
-      </c>
-      <c r="AE10" s="2" t="inlineStr"/>
-      <c r="AF10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6461,7 +5744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF10"/>
+  <dimension ref="A1:AF9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6841,12 +6124,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -6856,7 +6139,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -6867,74 +6150,82 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0.01525424958956756</v>
+        <v>0.008088979083777259</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.07188507109342634</v>
+        <v>-0.04988426630540721</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.2223141762956242</v>
+        <v>-0.2173480216895393</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.121880142964137</v>
+        <v>0.1154393212813815</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1646297036067336</v>
+        <v>0.1485841471395007</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1</v>
+        <v>0.9590643274853801</v>
       </c>
       <c r="P4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.2202351424839316</v>
+        <v>-0.2032134999970446</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.1298177948297481</v>
+        <v>0.154480812653065</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.7108227256560352</v>
+        <v>0.6558843076941773</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.2223141762956242</v>
+        <v>-0.2173480216895393</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.2628752641499237</v>
+        <v>0.2651933473772938</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.1785268977406829</v>
+        <v>-0.1770190346332644</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.489224968503877</v>
+        <v>0.4935390457433876</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.09340275911067697</v>
+        <v>-0.07769789874505406</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.06704235468052788</v>
+        <v>-0.04492675413271052</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.02299109383101428</v>
+        <v>0.04532217030697883</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.08801000229080636</v>
+        <v>-0.08633598999740544</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="inlineStr"/>
-      <c r="AE4" s="2" t="inlineStr"/>
-      <c r="AF4" s="2" t="inlineStr"/>
+      <c r="AE4" s="2" t="n">
+        <v>0.672706785284984</v>
+      </c>
+      <c r="AF4" s="2" t="n">
+        <v>-0.4013611977680653</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6944,7 +6235,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -6975,62 +6266,62 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.008088979083777259</v>
+        <v>-0.009208352324263647</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.04988426630540721</v>
+        <v>-0.06618686167416732</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.2173480216895393</v>
+        <v>-0.2400831038360258</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.1154393212813815</v>
+        <v>0.1339413127790688</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.1485841471395007</v>
+        <v>0.1702405031534576</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.9590643274853801</v>
+        <v>1</v>
       </c>
       <c r="P5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.2032134999970446</v>
+        <v>-0.2400831038360257</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.154480812653065</v>
+        <v>0.1010596638232772</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.6558843076941773</v>
+        <v>0.774883264895546</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.2173480216895393</v>
+        <v>-0.2400831038360258</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.2651933473772938</v>
+        <v>0.3038157891701148</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.1770190346332644</v>
+        <v>-0.1518959698484498</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.4935390457433876</v>
+        <v>0.5654174818173857</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.07769789874505406</v>
+        <v>-0.0934027591106773</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.04492675413271052</v>
+        <v>-0.06131441315437203</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.04532217030697883</v>
+        <v>-0.003047894074357016</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.08633598999740544</v>
+        <v>-0.05844465218910011</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -7039,7 +6330,7 @@
         <v>0.672706785284984</v>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>-0.4013611977680653</v>
+        <v>-0.04869290891591871</v>
       </c>
     </row>
     <row r="6">
@@ -7050,7 +6341,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -7068,94 +6359,84 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0.009208352324263647</v>
+        <v>0.195055031257702</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.06618686167416732</v>
+        <v>0.1263297301998034</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.2400831038360258</v>
+        <v>-0.08708938851250325</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.1339413127790688</v>
+        <v>0.03377704793948427</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1702405031534576</v>
+        <v>0.07867731439692574</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1</v>
+        <v>0.9103313840155945</v>
       </c>
       <c r="P6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.2400831038360257</v>
+        <v>-0.03443262266560088</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.1010596638232772</v>
+        <v>0.3990309956960505</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.774883264895546</v>
+        <v>0.1111334477259183</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.2400831038360258</v>
+        <v>-0.08708938851250325</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.3038157891701148</v>
+        <v>0.2376713001187341</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.1518959698484498</v>
+        <v>-0.1949215323571668</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.5654174818173857</v>
+        <v>0.4423190393773568</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.0934027591106773</v>
+        <v>-0.07769789874505395</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.06131441315437203</v>
+        <v>0.1322066914476954</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>-0.003047894074357016</v>
+        <v>0.2667496078925382</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.05844465218910011</v>
-      </c>
-      <c r="AB6" s="2" t="n">
-        <v>0.006139551516504582</v>
-      </c>
-      <c r="AC6" s="2" t="n">
-        <v>-0.02545377771360402</v>
-      </c>
-      <c r="AD6" s="2" t="n">
-        <v>0.03241850258881218</v>
-      </c>
+        <v>-0.1062111372338838</v>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
       <c r="AE6" s="2" t="n">
-        <v>0.672706785284984</v>
+        <v>0.06336097314022338</v>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>-0.04869290891591871</v>
+        <v>-0.06047836550494423</v>
       </c>
     </row>
     <row r="7">
@@ -7166,7 +6447,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -7197,62 +6478,62 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.195055031257702</v>
+        <v>0.04594236912116068</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.1263297301998034</v>
+        <v>-0.01420775143974151</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.08708938851250325</v>
+        <v>-0.2205813583428692</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.03377704793948427</v>
+        <v>0.1138724584051923</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.07867731439692574</v>
+        <v>0.1662598912357889</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9103313840155945</v>
+        <v>0.9766081871345029</v>
       </c>
       <c r="P7" t="b">
         <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.03443262266560088</v>
+        <v>-0.2184976920857807</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.3990309956960505</v>
+        <v>0.1323352234603714</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.1111334477259183</v>
+        <v>0.7052149956008925</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.08708938851250325</v>
+        <v>-0.2205813583428692</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.2376713001187341</v>
+        <v>0.3383739990643346</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.1949215323571668</v>
+        <v>-0.1294166001939632</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.4423190393773568</v>
+        <v>0.6297321643027176</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.07769789874505395</v>
+        <v>-0.08077573229096868</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.1322066914476954</v>
+        <v>-0.00906408641170986</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.2667496078925382</v>
+        <v>0.02527049417350136</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.1062111372338838</v>
+        <v>-0.03348831433297927</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -7261,7 +6542,7 @@
         <v>0.06336097314022338</v>
       </c>
       <c r="AF7" s="2" t="n">
-        <v>-0.06047836550494423</v>
+        <v>-0.004593434956671416</v>
       </c>
     </row>
     <row r="8">
@@ -7272,7 +6553,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -7290,94 +6571,84 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.04594236912116068</v>
+        <v>0.1624279055049469</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.01420775143974151</v>
+        <v>0.09557892727851836</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.2205813583428692</v>
+        <v>-0.1129718168111257</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.1138724584051923</v>
+        <v>0.04370498068554098</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1662598912357889</v>
+        <v>0.08021771111294687</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9766081871345029</v>
+        <v>0.6569200779727096</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.2184976920857807</v>
+        <v>-0.02968242544616717</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.1323352234603714</v>
+        <v>0.4059136569185156</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.7052149956008925</v>
+        <v>0.09580188848047258</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.2205813583428692</v>
+        <v>-0.08548640194113777</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.3383739990643346</v>
+        <v>0.1979870673160271</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.1294166001939632</v>
+        <v>-0.2207352692769127</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.6297321643027176</v>
+        <v>0.3684645532742738</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.08077573229096868</v>
+        <v>-0.07769789874505406</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.00906408641170986</v>
+        <v>0.1012954370420323</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.02527049417350136</v>
+        <v>0.2729814987024179</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.03348831433297927</v>
-      </c>
-      <c r="AB8" s="2" t="n">
-        <v>0.06214458776310749</v>
-      </c>
-      <c r="AC8" s="2" t="n">
-        <v>0.002228172225772651</v>
-      </c>
-      <c r="AD8" s="2" t="n">
-        <v>0.05978320825313754</v>
-      </c>
+        <v>-0.1348692513091431</v>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
       <c r="AE8" s="2" t="n">
         <v>0.06336097314022338</v>
       </c>
       <c r="AF8" s="2" t="n">
-        <v>-0.004593434956671416</v>
+        <v>-0.05953790568057138</v>
       </c>
     </row>
     <row r="9">
@@ -7388,7 +6659,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -7419,62 +6690,62 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.1624279055049469</v>
+        <v>0.02754756415532311</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.09557892727851836</v>
+        <v>-0.03154470678684806</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.1129718168111257</v>
+        <v>-0.2275727539629055</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.04370498068554098</v>
+        <v>0.1200355790004653</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.08021771111294687</v>
+        <v>0.1658988137626846</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.6569200779727096</v>
+        <v>0.98635477582846</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.02968242544616717</v>
+        <v>-0.2275727539629055</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.4059136569185156</v>
+        <v>0.1191861743603413</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.09580188848047258</v>
+        <v>0.7345053265909419</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.08548640194113777</v>
+        <v>-0.2275727539629055</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.1979870673160271</v>
+        <v>0.3302839450927095</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.2207352692769127</v>
+        <v>-0.1346790056920942</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.3684645532742738</v>
+        <v>0.6146761398712759</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.07769789874505406</v>
+        <v>-0.08077573229096868</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.1012954370420323</v>
+        <v>-0.0264915024933593</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.2729814987024179</v>
+        <v>0.01336471592922761</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.1348692513091431</v>
+        <v>-0.0393305764411187</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
@@ -7483,122 +6754,6 @@
         <v>0.06336097314022338</v>
       </c>
       <c r="AF9" s="2" t="n">
-        <v>-0.05953790568057138</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>hrp</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>0.02754756415532311</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>-0.03154470678684806</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>-0.2275727539629055</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>0.1200355790004653</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>0.1658988137626846</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>0.98635477582846</v>
-      </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>-0.2275727539629055</v>
-      </c>
-      <c r="R10" s="2" t="n">
-        <v>0.1191861743603413</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>0.7345053265909419</v>
-      </c>
-      <c r="T10" s="2" t="n">
-        <v>-0.2275727539629055</v>
-      </c>
-      <c r="U10" s="2" t="n">
-        <v>0.3302839450927095</v>
-      </c>
-      <c r="V10" s="2" t="n">
-        <v>-0.1346790056920942</v>
-      </c>
-      <c r="W10" s="3" t="n">
-        <v>0.6146761398712759</v>
-      </c>
-      <c r="X10" s="2" t="n">
-        <v>-0.08077573229096868</v>
-      </c>
-      <c r="Y10" s="2" t="n">
-        <v>-0.0264915024933593</v>
-      </c>
-      <c r="Z10" s="2" t="n">
-        <v>0.01336471592922761</v>
-      </c>
-      <c r="AA10" s="2" t="n">
-        <v>-0.0393305764411187</v>
-      </c>
-      <c r="AB10" s="2" t="n">
-        <v>0.04346483722021777</v>
-      </c>
-      <c r="AC10" s="2" t="n">
-        <v>-0.009410030996200303</v>
-      </c>
-      <c r="AD10" s="2" t="n">
-        <v>0.05337714884150535</v>
-      </c>
-      <c r="AE10" s="2" t="n">
-        <v>0.06336097314022338</v>
-      </c>
-      <c r="AF10" s="2" t="n">
         <v>-0.004259490730372684</v>
       </c>
     </row>
@@ -7613,7 +6768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF10"/>
+  <dimension ref="A1:AF9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7993,12 +7148,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -8008,7 +7163,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -8019,74 +7174,82 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0.06676653353273054</v>
+        <v>0.0148966629316607</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.06452511043579368</v>
+        <v>0.01733422320252243</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.1208786768201607</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.06599576241334662</v>
+        <v>0</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.2156952619322512</v>
+        <v>1.757200726823261e-05</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.1208786768201607</v>
+        <v>0.005700135266177409</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.13318215211393</v>
+        <v>0.2963414873615395</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.5391526104926985</v>
+        <v>-0.02542419299884719</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.1208786768201607</v>
+        <v>0</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.06155253189821752</v>
+        <v>0.009144403329576001</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.1744708581765999</v>
+        <v>-0.2152266720452529</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.2152897169169782</v>
+        <v>0.03198399714010954</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.04770980148098947</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.0182574470684671</v>
+        <v>0.06765056829770977</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.03592178902544596</v>
+        <v>0.1850772537056846</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.0523005082699175</v>
+        <v>-0.09908778945911489</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="inlineStr"/>
-      <c r="AE4" s="2" t="inlineStr"/>
-      <c r="AF4" s="2" t="inlineStr"/>
+      <c r="AE4" s="2" t="n">
+        <v>0.1212838470749049</v>
+      </c>
+      <c r="AF4" s="2" t="n">
+        <v>-0.09017125420230654</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8096,7 +7259,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -8127,62 +7290,62 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.0148966629316607</v>
+        <v>-0.06676653353273054</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.01733422320252243</v>
+        <v>-0.06452511043579368</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>-0.1208786768201607</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0</v>
+        <v>0.06599576241334662</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>1.757200726823261e-05</v>
+        <v>0.2156952619322512</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0.005700135266177409</v>
+        <v>-0.1208786768201607</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.2963414873615395</v>
+        <v>0.13318215211393</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.02542419299884719</v>
+        <v>0.5391526104926985</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>0</v>
+        <v>-0.1208786768201607</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.009144403329576001</v>
+        <v>0.06155253189821752</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.2152266720452529</v>
+        <v>-0.1744708581765999</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.03198399714010954</v>
+        <v>0.2152897169169782</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>0</v>
+        <v>-0.04770980148098947</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.06765056829770977</v>
+        <v>-0.0182574470684671</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.1850772537056846</v>
+        <v>0.03592178902544596</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.09908778945911489</v>
+        <v>-0.0523005082699175</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -8191,7 +7354,7 @@
         <v>0.1212838470749049</v>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>-0.09017125420230654</v>
+        <v>-0.03844538071637815</v>
       </c>
     </row>
     <row r="6">
@@ -8202,7 +7365,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -8220,95 +7383,81 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0.06676653353273054</v>
+        <v>0.006134762905609881</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.06452511043579368</v>
+        <v>0.008551279004999968</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.1208786768201607</v>
+        <v>-0.03420088913897812</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.06599576241334662</v>
+        <v>0.02209221769566901</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.2156952619322512</v>
+        <v>0.09940434955338903</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1</v>
+        <v>0.9431818181818182</v>
       </c>
       <c r="P6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.1208786768201607</v>
+        <v>-0.0263025305835507</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.13318215211393</v>
+        <v>0.2550902415951355</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.5391526104926985</v>
+        <v>0.1173166219198737</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.1208786768201607</v>
+        <v>-0.03420088913897812</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.06155253189821752</v>
+        <v>0.03331352345878091</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.1744708581765999</v>
+        <v>-0.1964312639996318</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.2152897169169782</v>
+        <v>0.1165193179511719</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.04770980148098947</v>
+        <v>-0.02658676130134163</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.0182574470684671</v>
+        <v>0.05843322836168241</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.03592178902544596</v>
+        <v>0.1473665783000193</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.0523005082699175</v>
-      </c>
-      <c r="AB6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="2" t="n">
-        <v>0.1212838470749049</v>
-      </c>
-      <c r="AF6" s="2" t="n">
-        <v>-0.03844538071637815</v>
-      </c>
+        <v>-0.07751084232390992</v>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8318,7 +7467,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -8349,62 +7498,62 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.006134762905609881</v>
+        <v>-0.05012584203506654</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.008551279004999968</v>
+        <v>-0.04784445162918494</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.03420088913897812</v>
+        <v>-0.1306426784263617</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.02209221769566901</v>
+        <v>0.06715753194681968</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.09940434955338903</v>
+        <v>0.2146821881986168</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9431818181818182</v>
+        <v>1</v>
       </c>
       <c r="P7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.0263025305835507</v>
+        <v>-0.1306426784263617</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.2550902415951355</v>
+        <v>0.1205964121692567</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.1173166219198737</v>
+        <v>0.5827027807404269</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.03420088913897812</v>
+        <v>-0.1306426784263617</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.03331352345878091</v>
+        <v>0.09261650462154081</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.1964312639996318</v>
+        <v>-0.150313584774355</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.1165193179511719</v>
+        <v>0.3239408753287847</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.02658676130134163</v>
+        <v>-0.04770980148098947</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.05843322836168241</v>
+        <v>-0.0007517793652872529</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.1473665783000193</v>
+        <v>0.02441627579849182</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.07751084232390992</v>
+        <v>-0.02456819142605038</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -8420,7 +7569,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -8438,40 +7587,36 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0.05012584203506654</v>
+        <v>-0.06067209613502056</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.04784445162918494</v>
+        <v>-0.05841603552963925</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.1306426784263617</v>
+        <v>-0.1002080841471648</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.06715753194681968</v>
+        <v>0.06554540773393126</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.2146821881986168</v>
+        <v>0.1149073497591276</v>
       </c>
       <c r="O8" s="2" t="n">
         <v>1</v>
@@ -8480,47 +7625,41 @@
         <v>0</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.1306426784263617</v>
+        <v>-0.07004650490199027</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.1205964121692567</v>
+        <v>0.1987045191093149</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.5827027807404269</v>
+        <v>0.3124269471445679</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.1306426784263617</v>
+        <v>-0.1002080841471648</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.09261650462154081</v>
+        <v>0.01008051350565831</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.150313584774355</v>
+        <v>-0.214498694665809</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.3239408753287847</v>
+        <v>0.0352581905582636</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.04770980148098947</v>
+        <v>-0.02080009568268082</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.0007517793652872529</v>
+        <v>-0.01184622335597174</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.02441627579849182</v>
+        <v>0.09582040948325976</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.02456819142605038</v>
-      </c>
-      <c r="AB8" s="2" t="n">
-        <v>0.0178312202633033</v>
-      </c>
-      <c r="AC8" s="2" t="n">
-        <v>-0.01110654621694751</v>
-      </c>
-      <c r="AD8" s="2" t="n">
-        <v>0.02926277484146378</v>
-      </c>
+        <v>-0.0982520784496087</v>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
     </row>
@@ -8532,7 +7671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -8563,23 +7702,23 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0.06067209613502056</v>
+        <v>-0.08871550606229961</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.05841603552963925</v>
+        <v>-0.08652679960674936</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.1002080841471648</v>
+        <v>-0.1441736393992464</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.06554540773393126</v>
+        <v>0.08747399177490939</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1149073497591276</v>
+        <v>0.2210157922397416</v>
       </c>
       <c r="O9" s="2" t="n">
         <v>1</v>
@@ -8588,155 +7727,43 @@
         <v>0</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.07004650490199027</v>
+        <v>-0.1441736393992464</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.1987045191093149</v>
+        <v>0.1031550840258753</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.3124269471445679</v>
+        <v>0.6430546403315049</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.1002080841471648</v>
+        <v>-0.1441736393992464</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.01008051350565831</v>
+        <v>0.06480068374853243</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.214498694665809</v>
+        <v>-0.1719448936775019</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.0352581905582636</v>
+        <v>0.2266506418179067</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.02080009568268082</v>
+        <v>-0.04770980148098947</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.01184622335597174</v>
+        <v>-0.0413473180382401</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.09582040948325976</v>
+        <v>0.008471926675479136</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.0982520784496087</v>
+        <v>-0.04940072539049545</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
       <c r="AE9" s="2" t="inlineStr"/>
       <c r="AF9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>hrp</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>-0.08871550606229961</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>-0.08652679960674936</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>-0.1441736393992464</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>0.08747399177490939</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>0.2210157922397416</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P10" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>-0.1441736393992464</v>
-      </c>
-      <c r="R10" s="2" t="n">
-        <v>0.1031550840258753</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>0.6430546403315049</v>
-      </c>
-      <c r="T10" s="2" t="n">
-        <v>-0.1441736393992464</v>
-      </c>
-      <c r="U10" s="2" t="n">
-        <v>0.06480068374853243</v>
-      </c>
-      <c r="V10" s="2" t="n">
-        <v>-0.1719448936775019</v>
-      </c>
-      <c r="W10" s="3" t="n">
-        <v>0.2266506418179067</v>
-      </c>
-      <c r="X10" s="2" t="n">
-        <v>-0.04770980148098947</v>
-      </c>
-      <c r="Y10" s="2" t="n">
-        <v>-0.0413473180382401</v>
-      </c>
-      <c r="Z10" s="2" t="n">
-        <v>0.008471926675479136</v>
-      </c>
-      <c r="AA10" s="2" t="n">
-        <v>-0.04940072539049545</v>
-      </c>
-      <c r="AB10" s="2" t="n">
-        <v>-0.02351927284890065</v>
-      </c>
-      <c r="AC10" s="2" t="n">
-        <v>-0.02649800654911461</v>
-      </c>
-      <c r="AD10" s="2" t="n">
-        <v>0.003059812635467729</v>
-      </c>
-      <c r="AE10" s="2" t="inlineStr"/>
-      <c r="AF10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_hrp_monthly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_hrp_monthly.xlsx
@@ -14,7 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C4" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C5" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C6" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C7" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -847,27 +848,27 @@
         <v>1.295281120905988</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="X3" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="Z3" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AB3" s="2" t="n">
@@ -966,19 +967,19 @@
         <v>1.212013900201544</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="X4" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="Z4" s="2" t="n">
@@ -986,7 +987,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AB4" s="2" t="n">
@@ -994,19 +995,19 @@
       </c>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AF4" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AH4" s="2" t="n">
@@ -1014,7 +1015,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ4" s="2" t="inlineStr"/>
@@ -1103,27 +1104,27 @@
         <v>1.314185608974349</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="X5" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AB5" s="2" t="n">
@@ -1131,19 +1132,19 @@
       </c>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AH5" s="2" t="n">
@@ -1151,7 +1152,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ5" s="2" t="inlineStr"/>
@@ -1240,11 +1241,11 @@
         <v>3.093572757198578</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="X6" s="2" t="n">
@@ -1252,7 +1253,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="Z6" s="2" t="n">
@@ -1260,7 +1261,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AB6" s="2" t="n">
@@ -1268,19 +1269,19 @@
       </c>
       <c r="AC6" s="2" t="inlineStr"/>
       <c r="AD6" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AH6" s="2" t="n">
@@ -1288,7 +1289,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ6" s="2" t="inlineStr"/>
@@ -1377,11 +1378,11 @@
         <v>1.962006680764288</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="X7" s="2" t="n">
@@ -1389,15 +1390,15 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AB7" s="2" t="n">
@@ -1405,27 +1406,27 @@
       </c>
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AF7" s="2" t="n">
-        <v>1</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AH7" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AJ7" s="2" t="inlineStr"/>
@@ -1514,11 +1515,11 @@
         <v>3.464272969689256</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="X8" s="2" t="n">
@@ -1526,7 +1527,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="Z8" s="2" t="n">
@@ -1534,7 +1535,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AB8" s="2" t="n">
@@ -1542,11 +1543,11 @@
       </c>
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AF8" s="2" t="n">
@@ -1554,7 +1555,7 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="AH8" s="2" t="n">
@@ -1562,7 +1563,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ8" s="2" t="inlineStr"/>
@@ -1651,27 +1652,27 @@
         <v>2.160975396310064</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="X9" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AB9" s="2" t="n">
@@ -1679,19 +1680,19 @@
       </c>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AF9" s="2" t="n">
-        <v>1</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AH9" s="2" t="n">
@@ -1699,7 +1700,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ9" s="2" t="inlineStr"/>
@@ -1950,28 +1951,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>-0.09343144196767172</v>
+        <v>0.05644008609220919</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.486230944244141</v>
+        <v>-0.1697286534192365</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.2715577666208222</v>
+        <v>0.08831268540851216</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.1809616537571158</v>
+        <v>0.2970580221997946</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9994459833795014</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="P2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.4704588408798223</v>
+        <v>-0.1697286534192365</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -1980,10 +1981,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.486230944244141</v>
+        <v>-0.1697286534192365</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.7119888462278816</v>
+        <v>0.2724034021441992</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -1992,7 +1993,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.1395291740668942</v>
+        <v>-0.08310591627222952</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -2038,49 +2039,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.3050913934539505</v>
+        <v>0.07488442474097812</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.4395948126489193</v>
+        <v>0.01745895379357942</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.3432461105733071</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.1109469294357623</v>
+        <v>0.07812037677756986</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.1530752451527519</v>
+        <v>0.2757884445827267</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9518005540166204</v>
+        <v>0.9111111111111111</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.2627477773058103</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.3922472502781837</v>
+        <v>0.01671906081640784</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.5584925916461387</v>
+        <v>0.918214415433338</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.3432461105733071</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.770210184900723</v>
+        <v>0.2733293632849492</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.03400801284489896</v>
+        <v>0.0007277260805729213</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>1.081772824084672</v>
+        <v>1.003399227518678</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.1175306843923517</v>
+        <v>-0.05422944133655971</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -2140,58 +2141,58 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.3842779105694654</v>
+        <v>-0.1083229862865027</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.5269423347021727</v>
+        <v>-0.155960640407137</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.08024052864543563</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.02021149327775454</v>
+        <v>0.09771466091861042</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.07840157698518678</v>
+        <v>0.2000900024958262</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.4875346260387812</v>
+        <v>1</v>
       </c>
       <c r="P4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>0.1023585420195272</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>1.081724003949144</v>
+        <v>0.01671906081640784</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>-0.2175717259943564</v>
+        <v>0.918214415433338</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.08024052864543563</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.2557419911977641</v>
+        <v>0.05629823820476032</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.2665010674779752</v>
+        <v>-0.1698401336991616</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.3591938168030099</v>
+        <v>0.2066723020403333</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.0753629105092779</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.06067507418461027</v>
+        <v>-0.1704438233641998</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.4952257966630542</v>
+        <v>0</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.2906254850927837</v>
+        <v>-0.1704438233641998</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -2242,58 +2243,58 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.3327651987937918</v>
+        <v>0.07211918692158736</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.4701206952141677</v>
+        <v>0.01484144821442301</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.3180206894883701</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.09243141147872172</v>
+        <v>0.07659835738414919</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.1485372500354234</v>
+        <v>0.2729068602764733</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.9484764542936288</v>
+        <v>0.9</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.222851313423697</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.4675888232512848</v>
+        <v>0.01671906081640784</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.4736892881148426</v>
+        <v>0.918214415433338</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.3180206894883701</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.7149423550662293</v>
+        <v>0.2700536078354787</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>0.001725191635947532</v>
+        <v>-0.001846736895516621</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>1.004148251554775</v>
+        <v>0.9913738437544307</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.1144491365988818</v>
+        <v>-0.04325670276229032</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.02120449608253261</v>
+        <v>-0.00257259083464445</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.05411508118119612</v>
+        <v>0</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.03122105516390605</v>
+        <v>-0.00257259083464445</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -2344,58 +2345,58 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.08107308521347445</v>
+        <v>-0.039036977793655</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.1924890573746585</v>
+        <v>-0.0903762221282568</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.4206842640084347</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.2178191233697231</v>
+        <v>0.09414950030062333</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1398884103485653</v>
+        <v>0.2101108942249834</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9950138504155125</v>
+        <v>1</v>
       </c>
       <c r="P6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.3041304927991617</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.3140989991354248</v>
+        <v>0.01671906081640784</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.6464550485020032</v>
+        <v>0.918214415433338</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.4206842640084347</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.5535572029332516</v>
+        <v>0.1383758151498473</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.09254245063787137</v>
+        <v>-0.105334194146679</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.7774801611935339</v>
+        <v>0.5079812295317693</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.1175306843923516</v>
+        <v>-0.01092907733707571</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.1716495176997583</v>
+        <v>-0.1059847923297293</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>-0.05613101489490768</v>
+        <v>0</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.1223882812422197</v>
+        <v>-0.1059847923297293</v>
       </c>
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr"/>
@@ -2446,58 +2447,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.3220281375575083</v>
+        <v>0.07633863832721954</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.4582770666864058</v>
+        <v>0.01883547632939164</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.3514343814258261</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.1146575544984008</v>
+        <v>0.07659524476889118</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1517987871375321</v>
+        <v>0.2730111050878728</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9523545706371191</v>
+        <v>0.9</v>
       </c>
       <c r="P7" t="b">
         <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.2560887104785098</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.4048224141018315</v>
+        <v>0.01671906081640784</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.5443381826975319</v>
+        <v>0.918214415433338</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.3514343814258261</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.7771314351310399</v>
+        <v>0.2750520534804977</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>0.03805082553352523</v>
+        <v>0.002081612900307395</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>1.091493833433324</v>
+        <v>1.009723268195073</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.1175306843923517</v>
+        <v>-0.04325670276229032</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.01297743911921323</v>
+        <v>0.001352902277462764</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.009032277723037385</v>
+        <v>0</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>0.003909846576046538</v>
+        <v>0.001352902277462764</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -2548,67 +2549,67 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.5514382080702624</v>
+        <v>0.01633146664688923</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.7113302621454229</v>
+        <v>-0.03796582501302315</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.0845172612821613</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.03285844017798271</v>
+        <v>0</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.08600622972498906</v>
+        <v>0.0002468489756377671</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.8288088642659279</v>
+        <v>0</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>0.03608271871848556</v>
+        <v>0.006089370624204005</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.9565669275640758</v>
+        <v>0.2117597153840092</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>-0.07669686608717131</v>
+        <v>-0.03587709265072067</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.0845172612821613</v>
+        <v>0</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.4974076683657191</v>
+        <v>0.01018010558677385</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.1253402896490599</v>
+        <v>-0.2060850325577077</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.6986172199199271</v>
+        <v>0.03737143334716839</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.07930571287241328</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.1887582860878043</v>
+        <v>-0.05447372456643307</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.4053300713455428</v>
+        <v>0.1918333806105563</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.1541074155272151</v>
+        <v>-0.2066623650453642</v>
       </c>
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr"/>
       <c r="AE8" s="2" t="n">
-        <v>-0.001279829547892186</v>
+        <v>0.08085941147512643</v>
       </c>
       <c r="AF8" s="2" t="n">
-        <v>0.009113158068361216</v>
+        <v>-0.0652324863726127</v>
       </c>
     </row>
     <row r="9">
@@ -2654,67 +2655,67 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.3937688239936334</v>
+        <v>0.06949778383754923</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.5374113867557402</v>
+        <v>0.01236009303058605</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.3272689968646514</v>
+        <v>-0.1581346033647496</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.09602380804475916</v>
+        <v>0.07842385788493024</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1495505253008701</v>
+        <v>0.2702499091159425</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9440443213296399</v>
+        <v>0.9</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.2111603173563172</v>
+        <v>-0.1581346033647495</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.4896664198007279</v>
+        <v>0.01396416978886927</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.4488390885830068</v>
+        <v>0.9316906731955904</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.3272689968646514</v>
+        <v>-0.1581346033647496</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.7668594198032961</v>
+        <v>0.2703904782309559</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>0.03205077748976803</v>
+        <v>-0.001581985642172379</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>1.077066619605235</v>
+        <v>0.9926105037697811</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.1144491365988818</v>
+        <v>-0.04325670276229021</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.06794729548020095</v>
+        <v>-0.005011367528864219</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.06997260687933049</v>
+        <v>-0.002709589240243337</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.001892862850981114</v>
+        <v>-0.002308032107585678</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
       <c r="AE9" s="2" t="n">
-        <v>-0.001279829547892186</v>
+        <v>0.08085941147512643</v>
       </c>
       <c r="AF9" s="2" t="n">
-        <v>-0.06347578376244911</v>
+        <v>-0.01981205682512033</v>
       </c>
     </row>
   </sheetData>
@@ -2958,28 +2959,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.05390587101818811</v>
+        <v>-0.09123360655355661</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.5040024023286778</v>
+        <v>-0.4862309442441412</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.2215345333965962</v>
+        <v>0.2716992530341495</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.2389368129070568</v>
+        <v>0.1810585772249194</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9832848837209303</v>
+        <v>1</v>
       </c>
       <c r="P2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.503509252857314</v>
+        <v>-0.4707583434268612</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -2988,10 +2989,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.5040024023286778</v>
+        <v>-0.4862309442441412</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>1.122709994261599</v>
+        <v>0.7171104771509156</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -3000,7 +3001,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.1530343433756423</v>
+        <v>-0.1395291740668942</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -3046,49 +3047,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.2553938843122963</v>
+        <v>0.3109354176354568</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.1911821718000761</v>
+        <v>0.442543900268815</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.4557974809248457</v>
+        <v>-0.343246110573307</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.1742196764528615</v>
+        <v>0.1110081735734261</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.2118070551778035</v>
+        <v>0.1531549489989729</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9491279069767442</v>
+        <v>0.9517470881863561</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.4557974809248456</v>
+        <v>-0.2609524087912378</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.09609800828525117</v>
+        <v>0.3964274769943947</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.9052415190749453</v>
+        <v>0.5543234919463098</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.4557974809248457</v>
+        <v>-0.343246110573307</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>1.306850557115716</v>
+        <v>0.7738173200609908</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.08674786633685749</v>
+        <v>0.03302457451902874</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>1.164014361496109</v>
+        <v>1.079076857355887</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.1243810385007439</v>
+        <v>-0.1175306843923517</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -3148,68 +3149,64 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.1906243837459807</v>
+        <v>0.3873890529214055</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.1297255442705785</v>
+        <v>0.5266729303884288</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.124381038500744</v>
+        <v>-0.08024052864543563</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.02820039558833212</v>
+        <v>0.02021124046371737</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.07209321945407876</v>
+        <v>0.07843898616176515</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.3292151162790697</v>
+        <v>0.4869661674986134</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>0.02220992715952153</v>
+        <v>0.1050430233370327</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>1.058870045499055</v>
+        <v>1.087974386771123</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>-0.04411026616389797</v>
+        <v>-0.223135765523299</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>0</v>
+        <v>-0.08024052864543563</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.1647552543873674</v>
+        <v>0.2555068206591071</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.4512885615387436</v>
+        <v>-0.2688258342338671</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.1467478291183522</v>
+        <v>0.3563004987379871</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.124381038500744</v>
+        <v>-0.0753629105092779</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.05159297123850193</v>
+        <v>0.05831990978155788</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.8783630933879494</v>
+        <v>0.4952257966630544</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.4950885523145134</v>
+        <v>-0.2922006079995104</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="inlineStr"/>
-      <c r="AE4" s="2" t="n">
-        <v>0.1213750437267103</v>
-      </c>
-      <c r="AF4" s="2" t="n">
-        <v>-0.0871167904264869</v>
-      </c>
+      <c r="AE4" s="2" t="inlineStr"/>
+      <c r="AF4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3254,68 +3251,64 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.3619902625519242</v>
+        <v>0.3377041486969667</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.2923262883392925</v>
+        <v>0.4720000193050735</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.3744774130256878</v>
+        <v>-0.3180206894883703</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.1204024944056784</v>
+        <v>0.09248235451518509</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.2016293480415229</v>
+        <v>0.1486155361074724</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.9280523255813954</v>
+        <v>0.9484193011647255</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.3743492138682257</v>
+        <v>-0.2209587883962083</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.2601459135591284</v>
+        <v>0.471995263275599</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.7434803069533858</v>
+        <v>0.4693677583869256</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.3744774130256878</v>
+        <v>-0.3180206894883703</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>1.176917687537377</v>
+        <v>0.7171160251497737</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>0.02553702268436098</v>
+        <v>3.231008681048309e-06</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>1.048282899014745</v>
+        <v>1.000007736602706</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.1243810385007439</v>
+        <v>-0.1144491365988818</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.0849107037812451</v>
+        <v>0.02041956506888254</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.1496653620696891</v>
+        <v>0.0541150811811959</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.05632478843397448</v>
+        <v>-0.03196569019253204</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
-      <c r="AE5" s="2" t="n">
-        <v>0.1213750437267103</v>
-      </c>
-      <c r="AF5" s="2" t="n">
-        <v>0.01477161720148734</v>
-      </c>
+      <c r="AE5" s="2" t="inlineStr"/>
+      <c r="AF5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3360,58 +3353,58 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.288558478756942</v>
+        <v>0.08591398546279971</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.2226504417439612</v>
+        <v>0.194931935526945</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.2686838800141741</v>
+        <v>-0.4206842640084347</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.1127733585915732</v>
+        <v>0.2179396869039446</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1149667393730911</v>
+        <v>0.1399607924165154</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9404069767441861</v>
+        <v>0.9950083194675541</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.2419911218891416</v>
+        <v>-0.3024359001414225</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.5267331415000467</v>
+        <v>0.3180445854835641</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.4806090861605632</v>
+        <v>0.6424440572627049</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.2421992389158157</v>
+        <v>-0.4206842640084347</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.6999253121788516</v>
+        <v>0.5567228670210458</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.1991721352543104</v>
+        <v>-0.09340552763733057</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.6234248521490975</v>
+        <v>0.7763418395906154</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.1243810385007441</v>
+        <v>-0.1175306843923516</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.02641768042610249</v>
+        <v>-0.1716495176997581</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.3928801347686841</v>
+        <v>-0.05613101489490768</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.2630969063274349</v>
+        <v>-0.1223882812422197</v>
       </c>
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr"/>
@@ -3462,58 +3455,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.3192077111603842</v>
+        <v>0.3279480022070416</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.2517320070395712</v>
+        <v>0.4612644259113461</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.4132656805387505</v>
+        <v>-0.3514343814258259</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.1480984800720592</v>
+        <v>0.1147208626995399</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.2046700509379647</v>
+        <v>0.1518777075181173</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9375</v>
+        <v>0.9523017193566279</v>
       </c>
       <c r="P7" t="b">
         <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.4132656805387506</v>
+        <v>-0.2542771256968984</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.1817628482261089</v>
+        <v>0.4090403977866885</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.8207707766908965</v>
+        <v>0.5401436411002323</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.4132656805387505</v>
+        <v>-0.3514343814258259</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>1.24839022945122</v>
+        <v>0.7807526736363632</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>0.05920744497805952</v>
+        <v>0.03706354211468366</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>1.111943632667383</v>
+        <v>1.088748105784618</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.1243810385007439</v>
+        <v>-0.1175306843923517</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.05083171715707779</v>
+        <v>0.01297743911921345</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.07815436146524224</v>
+        <v>0.009032277723037385</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.02534205238573839</v>
+        <v>0.003909846576046538</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -3564,64 +3557,68 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.1542976500171809</v>
+        <v>0.5542462466936398</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.09525687422350471</v>
+        <v>0.7102813857357244</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.1975522224118726</v>
+        <v>-0.08451726128216119</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.09525881742785987</v>
+        <v>0.03287661448338047</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1047304945378492</v>
+        <v>0.08604972206967795</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9534883720930233</v>
+        <v>0.8291735995562951</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.1428215242055786</v>
+        <v>0.03584725234815189</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.7264742207734993</v>
+        <v>0.9572292533722777</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.2836522335887476</v>
+        <v>-0.07614788531883186</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.1529693814334363</v>
+        <v>-0.08451726128216119</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.3466246325742062</v>
+        <v>0.5004589172489806</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.3656106410133336</v>
+        <v>-0.1261721728361999</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.3087392419644215</v>
+        <v>0.6978825901935041</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.1383494719981027</v>
+        <v>-0.07930571287241328</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.08052949401652998</v>
+        <v>0.185600927234878</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.5751093494590109</v>
+        <v>0.4015974947620813</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.4162497312968952</v>
+        <v>-0.1541074155272151</v>
       </c>
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr"/>
-      <c r="AE8" s="2" t="inlineStr"/>
-      <c r="AF8" s="2" t="inlineStr"/>
+      <c r="AE8" s="2" t="n">
+        <v>-0.003706020729931647</v>
+      </c>
+      <c r="AF8" s="2" t="n">
+        <v>0.01180051457259657</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3666,64 +3663,68 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.3403836730152192</v>
+        <v>0.3997387107985471</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.2718248468625213</v>
+        <v>0.540262405050125</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.4046464598524491</v>
+        <v>-0.3272689968646515</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.1428854981937125</v>
+        <v>0.09607685971570371</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.2036074392398008</v>
+        <v>0.1496284437807749</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.936046511627907</v>
+        <v>0.9439822518025514</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.4046464598524491</v>
+        <v>-0.2093925157785682</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.1991231328555914</v>
+        <v>0.4938496892717164</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.8036524801801787</v>
+        <v>0.4447983104331325</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.4046464598524491</v>
+        <v>-0.3272689968646515</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>1.251407915846141</v>
+        <v>0.7704597271514206</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>0.06062906470146912</v>
+        <v>0.03106920067777108</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>1.114631491874431</v>
+        <v>1.074394743488426</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.1243810385007439</v>
+        <v>-0.1144491365988818</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.06769969948474008</v>
+        <v>0.06774040274483184</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.09399262090760852</v>
+        <v>0.06976532178170003</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.02403391112552</v>
+        <v>-0.001892862850981003</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
-      <c r="AE9" s="2" t="inlineStr"/>
-      <c r="AF9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="n">
+        <v>-0.003706020729931647</v>
+      </c>
+      <c r="AF9" s="2" t="n">
+        <v>-0.06329431637923577</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3966,28 +3967,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.02340987064093203</v>
+        <v>0.05390587101818811</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.2022979914860074</v>
+        <v>-0.5040024023286778</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.0812675747870259</v>
+        <v>0.2215345333965962</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.2145128387962869</v>
+        <v>0.2389368129070568</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9517241379310345</v>
+        <v>0.9832848837209303</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.1954368693665688</v>
+        <v>-0.503509252857314</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -3996,10 +3997,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.2022979914860074</v>
+        <v>-0.5040024023286778</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.2720069211165606</v>
+        <v>1.122709994261599</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -4008,7 +4009,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.03286068493604632</v>
+        <v>-0.1530343433756423</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -4054,49 +4055,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.0189637709832835</v>
+        <v>0.2553938843122963</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.004344397865602034</v>
+        <v>0.1911821718000761</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.1452798889626855</v>
+        <v>-0.4557974809248457</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.04520489920804412</v>
+        <v>0.1742196764528615</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.165114162844639</v>
+        <v>0.2118070551778035</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9448275862068966</v>
+        <v>0.9491279069767442</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.1425767900867722</v>
+        <v>-0.4557974809248456</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.06570035000010499</v>
+        <v>0.09609800828525117</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.7295286224594077</v>
+        <v>0.9052415190749453</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.1452798889626855</v>
+        <v>-0.4557974809248457</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.1884023656024003</v>
+        <v>1.306850557115716</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>-0.06572649419295029</v>
+        <v>0.08674786633685749</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.6926381315189625</v>
+        <v>1.164014361496109</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.02330447460112961</v>
+        <v>-0.1243810385007439</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -4156,64 +4157,68 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.0189637709832835</v>
+        <v>0.1906243837459807</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.004344397865602034</v>
+        <v>0.1297255442705785</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.1452798889626855</v>
+        <v>-0.124381038500744</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.04520489920804412</v>
+        <v>0.02820039558833212</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.165114162844639</v>
+        <v>0.07209321945407876</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9448275862068966</v>
+        <v>0.3292151162790697</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.1425767900867722</v>
+        <v>0.02220992715952153</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.06570035000010499</v>
+        <v>1.058870045499055</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.7295286224594077</v>
+        <v>-0.04411026616389797</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.1452798889626855</v>
+        <v>0</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.1884023656024003</v>
+        <v>0.1647552543873674</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.06572649419295029</v>
+        <v>-0.4512885615387436</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.6926381315189625</v>
+        <v>0.1467478291183522</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.02330447460112961</v>
+        <v>-0.124381038500744</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0</v>
+        <v>-0.05159297123850193</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0</v>
+        <v>0.8783630933879494</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>0</v>
+        <v>-0.4950885523145134</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="inlineStr"/>
-      <c r="AE4" s="2" t="inlineStr"/>
-      <c r="AF4" s="2" t="inlineStr"/>
+      <c r="AE4" s="2" t="n">
+        <v>0.1213750437267103</v>
+      </c>
+      <c r="AF4" s="2" t="n">
+        <v>-0.0871167904264869</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4258,64 +4263,68 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.0189637709832835</v>
+        <v>0.3619902625519242</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.004344397865602034</v>
+        <v>0.2923262883392925</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.1452798889626855</v>
+        <v>-0.3744774130256878</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.04520489920804412</v>
+        <v>0.1204024944056784</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.165114162844639</v>
+        <v>0.2016293480415229</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.9448275862068966</v>
+        <v>0.9280523255813954</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.1425767900867722</v>
+        <v>-0.3743492138682257</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.06570035000010499</v>
+        <v>0.2601459135591284</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.7295286224594077</v>
+        <v>0.7434803069533858</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.1452798889626855</v>
+        <v>-0.3744774130256878</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.1884023656024003</v>
+        <v>1.176917687537377</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.06572649419295029</v>
+        <v>0.02553702268436098</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.6926381315189625</v>
+        <v>1.048282899014745</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.02330447460112961</v>
+        <v>-0.1243810385007439</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0</v>
+        <v>0.0849107037812451</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0</v>
+        <v>0.1496653620696891</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0</v>
+        <v>-0.05632478843397448</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
-      <c r="AE5" s="2" t="inlineStr"/>
-      <c r="AF5" s="2" t="inlineStr"/>
+      <c r="AE5" s="2" t="n">
+        <v>0.1213750437267103</v>
+      </c>
+      <c r="AF5" s="2" t="n">
+        <v>0.01477161720148734</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4360,58 +4369,58 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.02101828569239994</v>
+        <v>0.288558478756942</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.002336878915418672</v>
+        <v>0.2226504417439612</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.05636256056298983</v>
+        <v>-0.2686838800141741</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.02273032266102984</v>
+        <v>0.1127733585915732</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.08866814164939027</v>
+        <v>0.1149667393730911</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9448275862068966</v>
+        <v>0.9404069767441861</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.02352288142809378</v>
+        <v>-0.2419911218891416</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.2136737086164107</v>
+        <v>0.5267331415000467</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.1203605108101347</v>
+        <v>0.4806090861605632</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.05636256056298983</v>
+        <v>-0.2421992389158157</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.04561414320249013</v>
+        <v>0.6999253121788516</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.1779807752267135</v>
+        <v>-0.1991721352543104</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.167694788850404</v>
+        <v>0.6234248521490975</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.01299965782681711</v>
+        <v>-0.1243810385007441</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.002016278466047794</v>
+        <v>0.02641768042610249</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.1388508116904448</v>
+        <v>0.3928801347686841</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.1201514121250767</v>
+        <v>-0.2630969063274349</v>
       </c>
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr"/>
@@ -4462,58 +4471,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.009997036596348874</v>
+        <v>0.3192077111603842</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.01310602372457392</v>
+        <v>0.2517320070395712</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.1437296698623749</v>
+        <v>-0.4132656805387505</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.04713651623559876</v>
+        <v>0.1480984800720592</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1582645991808558</v>
+        <v>0.2046700509379647</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9724137931034482</v>
+        <v>0.9375</v>
       </c>
       <c r="P7" t="b">
         <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.1418475533411728</v>
+        <v>-0.4132656805387506</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.06660672604175288</v>
+        <v>0.1817628482261089</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.725797306316436</v>
+        <v>0.8207707766908965</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.1437296698623749</v>
+        <v>-0.4132656805387505</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.1769436077805531</v>
+        <v>1.24839022945122</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.0747349025841475</v>
+        <v>0.05920744497805952</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.6505114173353299</v>
+        <v>1.111943632667383</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.02128572850164578</v>
+        <v>-0.1243810385007439</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.00879985593431043</v>
+        <v>0.05083171715707779</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.0008504980238090987</v>
+        <v>0.07815436146524224</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.009642153325770897</v>
+        <v>-0.02534205238573839</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -4564,58 +4573,58 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.03628551780779454</v>
+        <v>0.1542976500171809</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.01258112466591599</v>
+        <v>0.09525687422350471</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.05636256056298983</v>
+        <v>-0.1975522224118726</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.02181766856855238</v>
+        <v>0.09525881742785987</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.09381119840717209</v>
+        <v>0.1047304945378492</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9172413793103448</v>
+        <v>0.9534883720930233</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.02352288142809378</v>
+        <v>-0.1428215242055786</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.2136737086164107</v>
+        <v>0.7264742207734993</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.1203605108101347</v>
+        <v>0.2836522335887476</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.05636256056298983</v>
+        <v>-0.1529693814334363</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.06124915586691659</v>
+        <v>0.3466246325742062</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.1656891654839755</v>
+        <v>-0.3656106410133336</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.2251749904579453</v>
+        <v>0.3087392419644215</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.01241008337108096</v>
+        <v>-0.1383494719981027</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.01699937457815182</v>
+        <v>-0.08052949401652998</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.1388508116904448</v>
+        <v>0.5751093494590109</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.1069950829919712</v>
+        <v>-0.4162497312968952</v>
       </c>
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr"/>
@@ -4666,58 +4675,58 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.0133351018917065</v>
+        <v>0.3403836730152192</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.009844314617481698</v>
+        <v>0.2718248468625213</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.1437296698623749</v>
+        <v>-0.4046464598524491</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.04678736816659274</v>
+        <v>0.1428854981937125</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1585358318065773</v>
+        <v>0.2036074392398008</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9586206896551724</v>
+        <v>0.936046511627907</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.1418475533411728</v>
+        <v>-0.4046464598524491</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.06660672604175288</v>
+        <v>0.1991231328555914</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.725797306316436</v>
+        <v>0.8036524801801787</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.1437296698623749</v>
+        <v>-0.4046464598524491</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.1808334356408061</v>
+        <v>1.251407915846141</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.07167687845261317</v>
+        <v>0.06062906470146912</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.6648118911772664</v>
+        <v>1.114631491874431</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.02128572850164578</v>
+        <v>-0.1243810385007439</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.005523914835701582</v>
+        <v>0.06769969948474008</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.0008504980238090987</v>
+        <v>0.09399262090760852</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.006368996040964192</v>
+        <v>-0.02403391112552</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
@@ -4966,28 +4975,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.09782647207714601</v>
+        <v>0.01891210187562598</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.2902196151348785</v>
+        <v>-0.2022979914860074</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.1130717188570335</v>
+        <v>0.08099293800752018</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.459050197355985</v>
+        <v>0.2138559415886583</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9098360655737705</v>
+        <v>0.9657534246575342</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.2902196151348786</v>
+        <v>-0.1989728318606706</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -4996,10 +5005,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.2902196151348785</v>
+        <v>-0.2022979914860074</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.5467128924473792</v>
+        <v>0.2720069211165606</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -5008,7 +5017,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.05185156587886086</v>
+        <v>-0.03286068493604632</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -5054,49 +5063,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>-0.0009544101684616502</v>
+        <v>0.01970412365980478</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.08997859384708495</v>
+        <v>0.0007773210100467942</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.1452798889626854</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.1202708276706985</v>
+        <v>0.04505087866076889</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.428252010780779</v>
+        <v>0.1645456863596117</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>1</v>
+        <v>0.9383561643835616</v>
       </c>
       <c r="P3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.1419538085967058</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-0.00807433626786469</v>
+        <v>0.07118238373413943</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>1.019747133566668</v>
+        <v>0.7134331218450367</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.1452798889626854</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.4189993189650008</v>
+        <v>0.1884023656024003</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>-0.08257096330288938</v>
+        <v>-0.06572649419295029</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.7663973627717755</v>
+        <v>0.6926381315189625</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.07538615706116925</v>
+        <v>-0.02330447460112961</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -5156,58 +5165,58 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0.2274421683855108</v>
+        <v>0.01970412365980478</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.2962842022266335</v>
+        <v>0.0007773210100467942</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.1452798889626854</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.2150465200281015</v>
+        <v>0.04505087866076889</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.376471579977516</v>
+        <v>0.1645456863596117</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1</v>
+        <v>0.9383561643835616</v>
       </c>
       <c r="P4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.1419538085967058</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>-0.00807433626786469</v>
+        <v>0.07118238373413943</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>1.019747133566668</v>
+        <v>0.7134331218450367</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.1452798889626854</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.09730631722911864</v>
+        <v>0.1884023656024003</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.2905559120976615</v>
+        <v>-0.06572649419295029</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.17798431054648</v>
+        <v>0.6926381315189625</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.05119781779615939</v>
+        <v>-0.02330447460112961</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.2267041269410339</v>
+        <v>0</v>
       </c>
       <c r="Z4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.2267041269410338</v>
+        <v>0</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -5258,58 +5267,58 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0.01329447775510906</v>
+        <v>0.01970412365980478</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.1012190475075795</v>
+        <v>0.0007773210100467942</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.1452798889626854</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.1283082103708132</v>
+        <v>0.04505087866076889</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.4246186257165711</v>
+        <v>0.1645456863596117</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>1</v>
+        <v>0.9383561643835616</v>
       </c>
       <c r="P5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.1419538085967058</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.00807433626786469</v>
+        <v>0.07118238373413943</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>1.019747133566668</v>
+        <v>0.7134331218450367</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.1452798889626854</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.4014720432534016</v>
+        <v>0.1884023656024003</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.09390291495156644</v>
+        <v>-0.06572649419295029</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.7343379839758271</v>
+        <v>0.6926381315189625</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.0790522597965585</v>
+        <v>-0.02330447460112961</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.01235185632392233</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.01235185632392222</v>
+        <v>0</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -5360,68 +5369,64 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.02943958852926998</v>
+        <v>0.02176013112608022</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.06229298098312785</v>
+        <v>0.002795166771708324</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.07538615706116925</v>
+        <v>-0.05636256056298983</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.02800300401528761</v>
+        <v>0.02265287670279683</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1136941935630939</v>
+        <v>0.08836517841517642</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.4180327868852459</v>
+        <v>0.9383561643835616</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>0.0007182735616988456</v>
+        <v>-0.02281339845246377</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.4098984628208118</v>
+        <v>0.2199169271841301</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.002474931135736743</v>
+        <v>0.1146558464244943</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>0</v>
+        <v>-0.05636256056298983</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.02870070001354907</v>
+        <v>0.04561414320249013</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.3349116665176135</v>
+        <v>-0.1779807752267135</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.0524968414135423</v>
+        <v>0.167694788850404</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.07538615706116913</v>
+        <v>-0.01299965782681711</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.0304230347514538</v>
+        <v>0.002016278466047794</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.4213751235309786</v>
+        <v>0.1388508116904446</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.2750520128763206</v>
+        <v>-0.1201514121250767</v>
       </c>
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr"/>
       <c r="AD6" s="2" t="inlineStr"/>
-      <c r="AE6" s="2" t="n">
-        <v>0.02027751002917078</v>
-      </c>
-      <c r="AF6" s="2" t="n">
-        <v>-0.0192674312508917</v>
-      </c>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5466,68 +5471,64 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0.007407262005415527</v>
+        <v>0.01073087427597597</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.0958564370227416</v>
+        <v>-0.008029375237167069</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.2893340076613283</v>
+        <v>-0.1437296698623748</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.1198547310511575</v>
+        <v>0.04697591435052775</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.4118484759031685</v>
+        <v>0.1577202819982108</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>1</v>
+        <v>0.9657534246575342</v>
       </c>
       <c r="P7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.2893340076613283</v>
+        <v>-0.1412240420065803</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.00124772041103749</v>
+        <v>0.07209342223464454</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.9969484920130616</v>
+        <v>0.7097654523280421</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.2893340076613283</v>
+        <v>-0.1437296698623748</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.3967078046441248</v>
+        <v>0.1769436077805531</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.09698314957852316</v>
+        <v>-0.0747349025841475</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.7256236502275419</v>
+        <v>0.6505114173353299</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.07538615706116902</v>
+        <v>-0.02128572850164578</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.006459016387872718</v>
+        <v>-0.008799855934310652</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.009397938796973815</v>
+        <v>0.0008504980238090987</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.01570931995734504</v>
+        <v>-0.009642153325770897</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr"/>
-      <c r="AE7" s="2" t="n">
-        <v>0.02027751002917078</v>
-      </c>
-      <c r="AF7" s="2" t="n">
-        <v>-0.004450505083797629</v>
-      </c>
+      <c r="AE7" s="2" t="inlineStr"/>
+      <c r="AF7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5572,58 +5573,58 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0.03877647638945059</v>
+        <v>0.03703845601678402</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.1244303648536882</v>
+        <v>0.017789909559216</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.1195800593377413</v>
+        <v>-0.05636256056298983</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.07321180804657658</v>
+        <v>0.02174333217333708</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1191644851747677</v>
+        <v>0.09348928315022083</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1</v>
+        <v>0.910958904109589</v>
       </c>
       <c r="P8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.07487432247921966</v>
+        <v>-0.02281339845246377</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.3033970749932469</v>
+        <v>0.2199169271841301</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.2579919432544974</v>
+        <v>0.1146558464244943</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.1195800593377413</v>
+        <v>-0.05636256056298983</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.03901939700399049</v>
+        <v>0.06124915586691659</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.3282402945772698</v>
+        <v>-0.1656891654839755</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.07137091066083846</v>
+        <v>0.2251749904579453</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.005374568503844879</v>
+        <v>-0.01241008337108096</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.03785819847056893</v>
+        <v>0.01699937457815204</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.3140068078178315</v>
+        <v>0.1388508116904446</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.2677802003725855</v>
+        <v>-0.1069950829919712</v>
       </c>
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr"/>
@@ -5674,58 +5675,58 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0.008142625018193739</v>
+        <v>0.01407136492309435</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.09652627240336131</v>
+        <v>-0.0047508876807143</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.2918967743785572</v>
+        <v>-0.1437296698623748</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.1221338087310294</v>
+        <v>0.04662795588657805</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.4111036892321253</v>
+        <v>0.1579904129916729</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>1</v>
+        <v>0.952054794520548</v>
       </c>
       <c r="P9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.2918967743785572</v>
+        <v>-0.1412240420065803</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>-0.002362927011567595</v>
+        <v>0.07209342223464454</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>1.005778931389249</v>
+        <v>0.7097654523280421</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.2918967743785572</v>
+        <v>-0.1437296698623748</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.40072427167852</v>
+        <v>0.1808334356408061</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.09438637350326862</v>
+        <v>-0.07167687845261317</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.7329702248005602</v>
+        <v>0.6648118911772664</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.0790522597965585</v>
+        <v>-0.02128572850164578</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.007195081909069034</v>
+        <v>-0.005523914835701582</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.005757900480977352</v>
+        <v>0.0008504980238090987</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.01287882738365964</v>
+        <v>-0.006368996040964192</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
@@ -5974,28 +5975,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.06101703543393744</v>
+        <v>0.1113578145363066</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.3239608533428741</v>
+        <v>-0.2902196151348785</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.1799741913752891</v>
+        <v>0.1112768582964018</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.240579627043532</v>
+        <v>0.4518304992174232</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9746588693957114</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.3098313187450097</v>
+        <v>-0.2902196151348786</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -6004,10 +6005,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.3098313187450098</v>
+        <v>-0.2902196151348785</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.5373300241682992</v>
+        <v>0.5657770181230022</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -6016,7 +6017,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.1055402030174765</v>
+        <v>-0.05185156587886086</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -6062,49 +6063,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.05550959933794908</v>
+        <v>0.001402698831345583</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.005190714109256422</v>
+        <v>-0.09893763670599443</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.2377598766809245</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.1161134555088488</v>
+        <v>0.1183626651723915</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.1734081721485486</v>
+        <v>0.4213989939818436</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9727095516569201</v>
+        <v>0.9920634920634921</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.2377598766809244</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.1044258367867865</v>
+        <v>-0.00807433626786469</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.7673849036436503</v>
+        <v>1.019747133566668</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.2377598766809245</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.3847468363930642</v>
+        <v>0.4223472503301919</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>-0.09925207039248651</v>
+        <v>-0.09160293332491798</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.7160345022383415</v>
+        <v>0.7464906434894674</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.07769789874505417</v>
+        <v>-0.07538615706116925</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -6164,68 +6165,64 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.008088979083777259</v>
+        <v>-0.2274294276362275</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.04988426630540721</v>
+        <v>-0.3048408332053586</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.2173480216895393</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1154393212813815</v>
+        <v>0.2154475431662235</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1485841471395007</v>
+        <v>0.3704463949765835</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9590643274853801</v>
+        <v>1</v>
       </c>
       <c r="P4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.2032134999970446</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.154480812653065</v>
+        <v>-0.00807433626786469</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.6558843076941773</v>
+        <v>1.019747133566668</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.2173480216895393</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.2651933473772938</v>
+        <v>0.09732441361504951</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.1770190346332644</v>
+        <v>-0.2991821945819061</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.4935390457433876</v>
+        <v>0.1720190295779932</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.07769789874505406</v>
+        <v>-0.05119781779615939</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.04492675413271052</v>
+        <v>-0.2285115935223904</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.04532217030697883</v>
+        <v>0</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.08633598999740544</v>
+        <v>-0.2285115935223904</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="inlineStr"/>
-      <c r="AE4" s="2" t="n">
-        <v>0.672706785284984</v>
-      </c>
-      <c r="AF4" s="2" t="n">
-        <v>-0.4013611977680653</v>
-      </c>
+      <c r="AE4" s="2" t="inlineStr"/>
+      <c r="AF4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6270,19 +6267,19 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0.009208352324263647</v>
+        <v>-0.01072905886483844</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.06618686167416732</v>
+        <v>-0.1098537948843087</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.2400831038360258</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.1339413127790688</v>
+        <v>0.1263011937639014</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.1702405031534576</v>
+        <v>0.4178848362006169</v>
       </c>
       <c r="O5" s="2" t="n">
         <v>1</v>
@@ -6291,47 +6288,43 @@
         <v>0</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.2400831038360257</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.1010596638232772</v>
+        <v>-0.00807433626786469</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.774883264895546</v>
+        <v>1.019747133566668</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.2400831038360258</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.3038157891701148</v>
+        <v>0.4051158485964268</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.1518959698484498</v>
+        <v>-0.1026079497061275</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.5654174818173857</v>
+        <v>0.7160344722739392</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.0934027591106773</v>
+        <v>-0.0790522597965585</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.06131441315437203</v>
+        <v>-0.01211476433041569</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>-0.003047894074357016</v>
+        <v>0</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.05844465218910011</v>
+        <v>-0.01211476433041581</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
-      <c r="AE5" s="2" t="n">
-        <v>0.672706785284984</v>
-      </c>
-      <c r="AF5" s="2" t="n">
-        <v>-0.04869290891591871</v>
-      </c>
+      <c r="AE5" s="2" t="inlineStr"/>
+      <c r="AF5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6376,67 +6369,67 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.195055031257702</v>
+        <v>0.03186840793809131</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.1263297301998034</v>
+        <v>-0.07152458511427373</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.08708938851250325</v>
+        <v>-0.07538615706116925</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.03377704793948427</v>
+        <v>0.02766429674434478</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.07867731439692574</v>
+        <v>0.1120581431927667</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9103313840155945</v>
+        <v>0.4365079365079365</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.03443262266560088</v>
+        <v>0.0007182735616988456</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.3990309956960505</v>
+        <v>0.4098984628208118</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.1111334477259183</v>
+        <v>-0.002474931135736743</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.08708938851250325</v>
+        <v>0</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.2376713001187341</v>
+        <v>0.03112777611777262</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.1949215323571668</v>
+        <v>-0.3414593750048446</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.4423190393773568</v>
+        <v>0.05501774572081562</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.07769789874505395</v>
+        <v>-0.07538615706116913</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.1322066914476954</v>
+        <v>0.0304230347514538</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.2667496078925382</v>
+        <v>0.4213751235309786</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.1062111372338838</v>
+        <v>-0.2750520128763208</v>
       </c>
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr"/>
       <c r="AD6" s="2" t="inlineStr"/>
       <c r="AE6" s="2" t="n">
-        <v>0.06336097314022338</v>
+        <v>0.02027751002917078</v>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>-0.06047836550494423</v>
+        <v>-0.0192674312508917</v>
       </c>
     </row>
     <row r="7">
@@ -6482,67 +6475,67 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.04594236912116068</v>
+        <v>-0.005065377611265909</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.01420775143974151</v>
+        <v>-0.1047576132770055</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.2205813583428692</v>
+        <v>-0.2893340076613283</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.1138724584051923</v>
+        <v>0.1179622320402137</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1662598912357889</v>
+        <v>0.405262867083531</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9766081871345029</v>
+        <v>1</v>
       </c>
       <c r="P7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.2184976920857807</v>
+        <v>-0.2893340076613283</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.1323352234603714</v>
+        <v>0.00124772041103749</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.7052149956008925</v>
+        <v>0.9969484920130616</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.2205813583428692</v>
+        <v>-0.2893340076613283</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.3383739990643346</v>
+        <v>0.4000031422843049</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.1294166001939632</v>
+        <v>-0.1058732334936306</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.6297321643027176</v>
+        <v>0.7069978621813561</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.08077573229096868</v>
+        <v>-0.07538615706116902</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.00906408641170986</v>
+        <v>-0.006459016387872607</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.02527049417350136</v>
+        <v>0.009397938796973815</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.03348831433297927</v>
+        <v>-0.01570931995734515</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr"/>
       <c r="AE7" s="2" t="n">
-        <v>0.06336097314022338</v>
+        <v>0.02027751002917078</v>
       </c>
       <c r="AF7" s="2" t="n">
-        <v>-0.004593434956671416</v>
+        <v>-0.004450505083797629</v>
       </c>
     </row>
     <row r="8">
@@ -6588,68 +6581,64 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.1624279055049469</v>
+        <v>-0.03650860328997474</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.09557892727851836</v>
+        <v>-0.1330502344899386</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.1129718168111257</v>
+        <v>-0.1195800593377413</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.04370498068554098</v>
+        <v>0.07239563403299919</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.08021771111294687</v>
+        <v>0.117454756465206</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.6569200779727096</v>
+        <v>1</v>
       </c>
       <c r="P8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.02968242544616717</v>
+        <v>-0.07487432247921966</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.4059136569185156</v>
+        <v>0.3033970749932469</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.09580188848047258</v>
+        <v>0.2579919432544974</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.08548640194113777</v>
+        <v>-0.1195800593377413</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.1979870673160271</v>
+        <v>0.04147081863737712</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.2207352692769127</v>
+        <v>-0.3348536818570403</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.3684645532742738</v>
+        <v>0.07329887448408376</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.07769789874505406</v>
+        <v>-0.005374568503844879</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.1012954370420323</v>
+        <v>-0.03785819847056882</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.2729814987024179</v>
+        <v>0.3140068078178315</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.1348692513091431</v>
+        <v>-0.2677802003725855</v>
       </c>
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr"/>
-      <c r="AE8" s="2" t="n">
-        <v>0.06336097314022338</v>
-      </c>
-      <c r="AF8" s="2" t="n">
-        <v>-0.05953790568057138</v>
-      </c>
+      <c r="AE8" s="2" t="inlineStr"/>
+      <c r="AF8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6694,68 +6683,64 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.02754756415532311</v>
+        <v>-0.005802475610708679</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.03154470678684806</v>
+        <v>-0.105420854215074</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.2275727539629055</v>
+        <v>-0.2918967743785572</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.1200355790004653</v>
+        <v>0.1202066398396258</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1658988137626846</v>
+        <v>0.4045302747050755</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.98635477582846</v>
+        <v>1</v>
       </c>
       <c r="P9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.2275727539629055</v>
+        <v>-0.2918967743785572</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.1191861743603413</v>
+        <v>-0.002362927011567595</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.7345053265909419</v>
+        <v>1.005778931389249</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.2275727539629055</v>
+        <v>-0.2918967743785572</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.3302839450927095</v>
+        <v>0.4040290856135664</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.1346790056920942</v>
+        <v>-0.1033020223424491</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.6146761398712759</v>
+        <v>0.7141136395994948</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.08077573229096868</v>
+        <v>-0.0790522597965585</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.0264915024933593</v>
+        <v>-0.007195081909068923</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.01336471592922761</v>
+        <v>0.005757900480977352</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.0393305764411187</v>
+        <v>-0.01287882738365964</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
-      <c r="AE9" s="2" t="n">
-        <v>0.06336097314022338</v>
-      </c>
-      <c r="AF9" s="2" t="n">
-        <v>-0.004259490730372684</v>
-      </c>
+      <c r="AE9" s="2" t="inlineStr"/>
+      <c r="AF9" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6998,28 +6983,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>-0.002396027003975565</v>
+        <v>0.06101703543393744</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.2242012270138081</v>
+        <v>-0.3239608533428741</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.1038210158252798</v>
+        <v>0.1799741913752891</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.3353086213004998</v>
+        <v>0.240579627043532</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>1</v>
+        <v>0.9746588693957114</v>
       </c>
       <c r="P2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.2242012270138081</v>
+        <v>-0.3098313187450097</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -7028,10 +7013,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.2242012270138081</v>
+        <v>-0.3098313187450098</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.2859055823922789</v>
+        <v>0.5373300241682992</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -7040,7 +7025,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.07899825662835758</v>
+        <v>-0.1055402030174765</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -7086,49 +7071,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>-0.04941120899711726</v>
+        <v>0.05550959933794908</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.04712810219865582</v>
+        <v>-0.005190714109256422</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.1513632279065376</v>
+        <v>-0.2377598766809245</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.07294179359961758</v>
+        <v>0.1161134555088488</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.2326154609655196</v>
+        <v>0.1734081721485486</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>1</v>
+        <v>0.9727095516569201</v>
       </c>
       <c r="P3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.1513632279065376</v>
+        <v>-0.2377598766809244</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.09388774724005255</v>
+        <v>0.1044258367867865</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.6751222101795875</v>
+        <v>0.7673849036436503</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.1513632279065376</v>
+        <v>-0.2377598766809245</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.1201362258412626</v>
+        <v>0.3847468363930642</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>-0.1289125413411937</v>
+        <v>-0.09925207039248651</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.4201954534641747</v>
+        <v>0.7160345022383415</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.04910852885624428</v>
+        <v>-0.07769789874505417</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -7188,67 +7173,67 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.0148966629316607</v>
+        <v>0.008088979083777259</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.01733422320252243</v>
+        <v>-0.04988426630540721</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>-0.2173480216895393</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0</v>
+        <v>0.1154393212813815</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>1.757200726823261e-05</v>
+        <v>0.1485841471395007</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0</v>
+        <v>0.9590643274853801</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>0.005700135266177409</v>
+        <v>-0.2032134999970446</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.2963414873615395</v>
+        <v>0.154480812653065</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>-0.02542419299884719</v>
+        <v>0.6558843076941773</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>0</v>
+        <v>-0.2173480216895393</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.009144403329576001</v>
+        <v>0.2651933473772938</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.2152266720452529</v>
+        <v>-0.1770190346332644</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.03198399714010954</v>
+        <v>0.4935390457433876</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>0</v>
+        <v>-0.07769789874505406</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.06765056829770977</v>
+        <v>-0.04492675413271052</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.1850772537056846</v>
+        <v>0.04532217030697883</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.09908778945911489</v>
+        <v>-0.08633598999740544</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="inlineStr"/>
       <c r="AE4" s="2" t="n">
-        <v>0.1212838470749049</v>
+        <v>0.672706785284984</v>
       </c>
       <c r="AF4" s="2" t="n">
-        <v>-0.09017125420230654</v>
+        <v>-0.4013611977680653</v>
       </c>
     </row>
     <row r="5">
@@ -7294,19 +7279,19 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0.06676653353273054</v>
+        <v>-0.009208352324263647</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.06452511043579368</v>
+        <v>-0.06618686167416732</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.1208786768201607</v>
+        <v>-0.2400831038360258</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.06599576241334662</v>
+        <v>0.1339413127790688</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.2156952619322512</v>
+        <v>0.1702405031534576</v>
       </c>
       <c r="O5" s="2" t="n">
         <v>1</v>
@@ -7315,46 +7300,46 @@
         <v>0</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.1208786768201607</v>
+        <v>-0.2400831038360257</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.13318215211393</v>
+        <v>0.1010596638232772</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.5391526104926985</v>
+        <v>0.774883264895546</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.1208786768201607</v>
+        <v>-0.2400831038360258</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.06155253189821752</v>
+        <v>0.3038157891701148</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.1744708581765999</v>
+        <v>-0.1518959698484498</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.2152897169169782</v>
+        <v>0.5654174818173857</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.04770980148098947</v>
+        <v>-0.0934027591106773</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.0182574470684671</v>
+        <v>-0.06131441315437203</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.03592178902544596</v>
+        <v>-0.003047894074357016</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.0523005082699175</v>
+        <v>-0.05844465218910011</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
       <c r="AE5" s="2" t="n">
-        <v>0.1212838470749049</v>
+        <v>0.672706785284984</v>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>-0.03844538071637815</v>
+        <v>-0.04869290891591871</v>
       </c>
     </row>
     <row r="6">
@@ -7400,64 +7385,68 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.006134762905609881</v>
+        <v>0.195055031257702</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.008551279004999968</v>
+        <v>0.1263297301998034</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.03420088913897812</v>
+        <v>-0.08708938851250325</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.02209221769566901</v>
+        <v>0.03377704793948427</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.09940434955338903</v>
+        <v>0.07867731439692574</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9431818181818182</v>
+        <v>0.9103313840155945</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.0263025305835507</v>
+        <v>-0.03443262266560088</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.2550902415951355</v>
+        <v>0.3990309956960505</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.1173166219198737</v>
+        <v>0.1111334477259183</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.03420088913897812</v>
+        <v>-0.08708938851250325</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.03331352345878091</v>
+        <v>0.2376713001187341</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.1964312639996318</v>
+        <v>-0.1949215323571668</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.1165193179511719</v>
+        <v>0.4423190393773568</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.02658676130134163</v>
+        <v>-0.07769789874505395</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.05843322836168241</v>
+        <v>0.1322066914476954</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.1473665783000193</v>
+        <v>0.2667496078925382</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.07751084232390992</v>
+        <v>-0.1062111372338838</v>
       </c>
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr"/>
       <c r="AD6" s="2" t="inlineStr"/>
-      <c r="AE6" s="2" t="inlineStr"/>
-      <c r="AF6" s="2" t="inlineStr"/>
+      <c r="AE6" s="2" t="n">
+        <v>0.06336097314022338</v>
+      </c>
+      <c r="AF6" s="2" t="n">
+        <v>-0.06047836550494423</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7502,64 +7491,68 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0.05012584203506654</v>
+        <v>0.04594236912116068</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.04784445162918494</v>
+        <v>-0.01420775143974151</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.1306426784263617</v>
+        <v>-0.2205813583428692</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.06715753194681968</v>
+        <v>0.1138724584051923</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.2146821881986168</v>
+        <v>0.1662598912357889</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>1</v>
+        <v>0.9766081871345029</v>
       </c>
       <c r="P7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.1306426784263617</v>
+        <v>-0.2184976920857807</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.1205964121692567</v>
+        <v>0.1323352234603714</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.5827027807404269</v>
+        <v>0.7052149956008925</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.1306426784263617</v>
+        <v>-0.2205813583428692</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.09261650462154081</v>
+        <v>0.3383739990643346</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.150313584774355</v>
+        <v>-0.1294166001939632</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.3239408753287847</v>
+        <v>0.6297321643027176</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.04770980148098947</v>
+        <v>-0.08077573229096868</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.0007517793652872529</v>
+        <v>-0.00906408641170986</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.02441627579849182</v>
+        <v>0.02527049417350136</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.02456819142605038</v>
+        <v>-0.03348831433297927</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr"/>
-      <c r="AE7" s="2" t="inlineStr"/>
-      <c r="AF7" s="2" t="inlineStr"/>
+      <c r="AE7" s="2" t="n">
+        <v>0.06336097314022338</v>
+      </c>
+      <c r="AF7" s="2" t="n">
+        <v>-0.004593434956671416</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7604,64 +7597,68 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0.06067209613502056</v>
+        <v>0.1624279055049469</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.05841603552963925</v>
+        <v>0.09557892727851836</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.1002080841471648</v>
+        <v>-0.1129718168111257</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.06554540773393126</v>
+        <v>0.04370498068554098</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1149073497591276</v>
+        <v>0.08021771111294687</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1</v>
+        <v>0.6569200779727096</v>
       </c>
       <c r="P8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.07004650490199027</v>
+        <v>-0.02968242544616717</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.1987045191093149</v>
+        <v>0.4059136569185156</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.3124269471445679</v>
+        <v>0.09580188848047258</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.1002080841471648</v>
+        <v>-0.08548640194113777</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.01008051350565831</v>
+        <v>0.1979870673160271</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.214498694665809</v>
+        <v>-0.2207352692769127</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.0352581905582636</v>
+        <v>0.3684645532742738</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.02080009568268082</v>
+        <v>-0.07769789874505406</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.01184622335597174</v>
+        <v>0.1012954370420323</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.09582040948325976</v>
+        <v>0.2729814987024179</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.0982520784496087</v>
+        <v>-0.1348692513091431</v>
       </c>
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr"/>
-      <c r="AE8" s="2" t="inlineStr"/>
-      <c r="AF8" s="2" t="inlineStr"/>
+      <c r="AE8" s="2" t="n">
+        <v>0.06336097314022338</v>
+      </c>
+      <c r="AF8" s="2" t="n">
+        <v>-0.05953790568057138</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7706,64 +7703,68 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0.08871550606229961</v>
+        <v>0.02754756415532311</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.08652679960674936</v>
+        <v>-0.03154470678684806</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.1441736393992464</v>
+        <v>-0.2275727539629055</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.08747399177490939</v>
+        <v>0.1200355790004653</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.2210157922397416</v>
+        <v>0.1658988137626846</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>1</v>
+        <v>0.98635477582846</v>
       </c>
       <c r="P9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.1441736393992464</v>
+        <v>-0.2275727539629055</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.1031550840258753</v>
+        <v>0.1191861743603413</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.6430546403315049</v>
+        <v>0.7345053265909419</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.1441736393992464</v>
+        <v>-0.2275727539629055</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.06480068374853243</v>
+        <v>0.3302839450927095</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.1719448936775019</v>
+        <v>-0.1346790056920942</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.2266506418179067</v>
+        <v>0.6146761398712759</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.04770980148098947</v>
+        <v>-0.08077573229096868</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.0413473180382401</v>
+        <v>-0.0264915024933593</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.008471926675479136</v>
+        <v>0.01336471592922761</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.04940072539049545</v>
+        <v>-0.0393305764411187</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
-      <c r="AE9" s="2" t="inlineStr"/>
-      <c r="AF9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="n">
+        <v>0.06336097314022338</v>
+      </c>
+      <c r="AF9" s="2" t="n">
+        <v>-0.004259490730372684</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7776,7 +7777,1015 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:AF9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="19" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="19" customWidth="1" min="22" max="22"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="11" customWidth="1" min="28" max="28"/>
+    <col width="10" customWidth="1" min="29" max="29"/>
+    <col width="10" customWidth="1" min="30" max="30"/>
+    <col width="14" customWidth="1" min="31" max="31"/>
+    <col width="17" customWidth="1" min="32" max="32"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>frequency</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>base_run</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>fallback_run</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>detector</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>crisis_target</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>full_cum_return</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>full_excess_return</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>full_max_dd</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>full_ulcer</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>full_ann_vol</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>full_underwater_share</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>full_recovered</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_cum_return</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_excess_return</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_down_capture</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_max_dd</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_cum_return</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_excess_return</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_recovery_capture</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_max_dd</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_base</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_base</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_base</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_fb</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_fb</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_fb</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>missed_rally</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>pre_peak_d_base</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>market_cap</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>mcap_t_10</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>benchmark</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" s="2" t="n">
+        <v>0.004925019651871976</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>-0.2242012270138081</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>0.1032426212645823</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>0.3336266559947869</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>0.9887640449438202</v>
+      </c>
+      <c r="P2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>-0.2242012270138081</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" s="2" t="n">
+        <v>-0.2242012270138081</v>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>0.2953423679490121</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" s="2" t="n">
+        <v>-0.07899825662835758</v>
+      </c>
+      <c r="Y2" s="2" t="inlineStr"/>
+      <c r="Z2" s="2" t="inlineStr"/>
+      <c r="AA2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AD2" s="2" t="inlineStr"/>
+      <c r="AE2" s="2" t="inlineStr"/>
+      <c r="AF2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" s="2" t="n">
+        <v>-0.04521242326464603</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>-0.04989172518949392</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>-0.1513632279065376</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>0.07269182521527755</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>0.2314419517208828</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>-0.1513632279065376</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>0.09388774724005255</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>0.6751222101795875</v>
+      </c>
+      <c r="T3" s="2" t="n">
+        <v>-0.1513632279065376</v>
+      </c>
+      <c r="U3" s="2" t="n">
+        <v>0.1250839088436306</v>
+      </c>
+      <c r="V3" s="2" t="n">
+        <v>-0.1314389641828525</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>0.4235217239987224</v>
+      </c>
+      <c r="X3" s="2" t="n">
+        <v>-0.04910852885624428</v>
+      </c>
+      <c r="Y3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="inlineStr"/>
+      <c r="AD3" s="2" t="inlineStr"/>
+      <c r="AE3" s="2" t="inlineStr"/>
+      <c r="AF3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>0.01506678954618668</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>0.0100920662696089</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>1.748592107069762e-05</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>0.005700135266177409</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>0.2963414873615395</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>-0.02542419299884719</v>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>0.00931356569573305</v>
+      </c>
+      <c r="V4" s="2" t="n">
+        <v>-0.2208132840633974</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>0.03153481080418825</v>
+      </c>
+      <c r="X4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="2" t="n">
+        <v>0.06313363755416845</v>
+      </c>
+      <c r="Z4" s="2" t="n">
+        <v>0.1850772537056846</v>
+      </c>
+      <c r="AA4" s="2" t="n">
+        <v>-0.1028992968772322</v>
+      </c>
+      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AD4" s="2" t="inlineStr"/>
+      <c r="AE4" s="2" t="n">
+        <v>0.1212838470749049</v>
+      </c>
+      <c r="AF4" s="2" t="n">
+        <v>-0.09017125420230654</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>min_var</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>-0.0633997631217984</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>-0.06798993102723183</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>-0.1208786768201607</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>0.06596747922643247</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>0.214593190060595</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>-0.1208786768201607</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>0.13318215211393</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>0.5391526104926985</v>
+      </c>
+      <c r="T5" s="2" t="n">
+        <v>-0.1208786768201607</v>
+      </c>
+      <c r="U5" s="2" t="n">
+        <v>0.06538223130620624</v>
+      </c>
+      <c r="V5" s="2" t="n">
+        <v>-0.1775284606855828</v>
+      </c>
+      <c r="W5" s="3" t="n">
+        <v>0.2213777581599597</v>
+      </c>
+      <c r="X5" s="2" t="n">
+        <v>-0.04770980148098947</v>
+      </c>
+      <c r="Y5" s="2" t="n">
+        <v>-0.01904857195496745</v>
+      </c>
+      <c r="Z5" s="2" t="n">
+        <v>0.03592178902544596</v>
+      </c>
+      <c r="AA5" s="2" t="n">
+        <v>-0.05306419998379164</v>
+      </c>
+      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AC5" s="2" t="inlineStr"/>
+      <c r="AD5" s="2" t="inlineStr"/>
+      <c r="AE5" s="2" t="n">
+        <v>0.1212838470749049</v>
+      </c>
+      <c r="AF5" s="2" t="n">
+        <v>-0.03844538071637815</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>0.01057889724362848</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>0.005626168600832759</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>-0.03420088913897812</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>0.02196915899737394</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>0.09910709621199867</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>0.9438202247191011</v>
+      </c>
+      <c r="P6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>-0.0263025305835507</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>0.2550902415951355</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>0.1173166219198737</v>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>-0.03420088913897812</v>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>0.03787770738408369</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>-0.1987618616787673</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>0.1282501648751692</v>
+      </c>
+      <c r="X6" s="2" t="n">
+        <v>-0.02658676130134163</v>
+      </c>
+      <c r="Y6" s="2" t="n">
+        <v>0.05843322836168263</v>
+      </c>
+      <c r="Z6" s="2" t="n">
+        <v>0.1473665783000193</v>
+      </c>
+      <c r="AA6" s="2" t="n">
+        <v>-0.07751084232390992</v>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>min_var</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>-0.0459302128630682</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>-0.05060599698528512</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>-0.1306426784263617</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>0.06695865383481796</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>0.2136241118637155</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>-0.1306426784263617</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>0.1205964121692567</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>0.5827027807404269</v>
+      </c>
+      <c r="T7" s="2" t="n">
+        <v>-0.1306426784263617</v>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>0.09744263200079106</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>-0.1527779379760169</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>0.329931098871712</v>
+      </c>
+      <c r="X7" s="2" t="n">
+        <v>-0.04770980148098947</v>
+      </c>
+      <c r="Y7" s="2" t="n">
+        <v>-0.0007517793652871418</v>
+      </c>
+      <c r="Z7" s="2" t="n">
+        <v>0.02441627579849182</v>
+      </c>
+      <c r="AA7" s="2" t="n">
+        <v>-0.0245681914260506</v>
+      </c>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AD7" s="2" t="inlineStr"/>
+      <c r="AE7" s="2" t="inlineStr"/>
+      <c r="AF7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>-0.05652305015615999</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>-0.06114692002525612</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>-0.1002080841471648</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>0.06545199237054125</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>0.1145767887415669</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>-0.07004650490199027</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>0.1987045191093149</v>
+      </c>
+      <c r="S8" s="3" t="n">
+        <v>0.3124269471445679</v>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>-0.1002080841471648</v>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>0.01454207636953386</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>-0.2167768912122322</v>
+      </c>
+      <c r="W8" s="3" t="n">
+        <v>0.04923802998709757</v>
+      </c>
+      <c r="X8" s="2" t="n">
+        <v>-0.02080009568268082</v>
+      </c>
+      <c r="Y8" s="2" t="n">
+        <v>-0.01184622335597174</v>
+      </c>
+      <c r="Z8" s="2" t="n">
+        <v>0.09582040948325976</v>
+      </c>
+      <c r="AA8" s="2" t="n">
+        <v>-0.0982520784496087</v>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
+      <c r="AE8" s="2" t="inlineStr"/>
+      <c r="AF8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>min_var</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>-0.08469032885888339</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>-0.08917615419884772</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>-0.1441736393992464</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>0.08744354902186333</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>0.2199486137693907</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>-0.1441736393992464</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>0.1031550840258753</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>0.6430546403315049</v>
+      </c>
+      <c r="T9" s="2" t="n">
+        <v>-0.1441736393992464</v>
+      </c>
+      <c r="U9" s="2" t="n">
+        <v>0.06950394762158107</v>
+      </c>
+      <c r="V9" s="2" t="n">
+        <v>-0.1743465093981398</v>
+      </c>
+      <c r="W9" s="3" t="n">
+        <v>0.2353334812890111</v>
+      </c>
+      <c r="X9" s="2" t="n">
+        <v>-0.04770980148098947</v>
+      </c>
+      <c r="Y9" s="2" t="n">
+        <v>-0.04134731803824021</v>
+      </c>
+      <c r="Z9" s="2" t="n">
+        <v>0.008471926675479136</v>
+      </c>
+      <c r="AA9" s="2" t="n">
+        <v>-0.04940072539049556</v>
+      </c>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AD9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="inlineStr"/>
+      <c r="AF9" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -7882,24 +8891,22 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>156</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>373</v>
-      </c>
+      <c r="E2" s="3" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr"/>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I2" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="J2" s="2" t="n">
-        <v>0.496398891966759</v>
+        <v>0.6444444444444445</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
         <v>2</v>
@@ -7930,20 +8937,20 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>-131</v>
+        <v>155</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>523</v>
+        <v>373</v>
       </c>
       <c r="G3" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.7274709302325582</v>
+        <v>0.4963948973932335</v>
       </c>
       <c r="K3" t="n">
         <v>3</v>
@@ -7976,20 +8983,24 @@
           <t>C3</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr"/>
-      <c r="F4" s="3" t="inlineStr"/>
+      <c r="E4" s="3" t="n">
+        <v>-131</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>523</v>
+      </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" s="3" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0</v>
+        <v>0.7274709302325582</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
         <v>2</v>
@@ -8025,16 +9036,14 @@
         <v>0</v>
       </c>
       <c r="H5" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="2" t="n">
-        <v>0.7540983606557377</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>2</v>
@@ -8064,24 +9073,22 @@
           <t>C5</t>
         </is>
       </c>
-      <c r="E6" s="3" t="n">
-        <v>-442</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>-174</v>
-      </c>
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>442</v>
+        <v>0</v>
       </c>
       <c r="H6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="J6" s="2" t="n">
-        <v>0.2787524366471735</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -8112,21 +9119,23 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>-114</v>
-      </c>
-      <c r="F7" s="3" t="inlineStr"/>
+        <v>-442</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>-174</v>
+      </c>
       <c r="G7" t="n">
-        <v>114</v>
+        <v>442</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="2" t="n">
-        <v>1</v>
+        <v>0.2787524366471735</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
         <v>2</v>
@@ -8143,37 +9152,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>changepoint</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>vix</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>156</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>18</v>
-      </c>
+        <v>-114</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
       </c>
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="2" t="n">
-        <v>0.08476454293628809</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>2</v>
@@ -8200,27 +9207,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>81</v>
-      </c>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="b">
-        <v>0</v>
-      </c>
-      <c r="I9" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="J9" s="2" t="n">
-        <v>0.3350290697674418</v>
+        <v>0.4777777777777778</v>
       </c>
       <c r="K9" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
         <v>2</v>
@@ -8247,14 +9252,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>30</v>
+        <v>155</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -8264,10 +9269,10 @@
       </c>
       <c r="I10" s="3" t="inlineStr"/>
       <c r="J10" s="2" t="n">
-        <v>0.5517241379310345</v>
+        <v>0.08485856905158069</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="L10" t="n">
         <v>2</v>
@@ -8294,27 +9299,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-10</v>
+        <v>39</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="G11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H11" t="b">
         <v>0</v>
       </c>
       <c r="I11" s="3" t="inlineStr"/>
       <c r="J11" s="2" t="n">
-        <v>0.7622950819672131</v>
+        <v>0.3350290697674418</v>
       </c>
       <c r="K11" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L11" t="n">
         <v>2</v>
@@ -8341,27 +9346,27 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>-21</v>
+        <v>31</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="G12" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H12" t="b">
         <v>0</v>
       </c>
       <c r="I12" s="3" t="inlineStr"/>
       <c r="J12" s="2" t="n">
-        <v>0.4892787524366471</v>
+        <v>0.547945205479452</v>
       </c>
       <c r="K12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L12" t="n">
         <v>2</v>
@@ -8388,27 +9393,27 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>9</v>
+        <v>-10</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H13" t="b">
         <v>0</v>
       </c>
       <c r="I13" s="3" t="inlineStr"/>
       <c r="J13" s="2" t="n">
-        <v>0.4772727272727273</v>
+        <v>0.7380952380952381</v>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L13" t="n">
         <v>2</v>
@@ -8425,37 +9430,37 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>-35</v>
+        <v>-21</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>141</v>
+        <v>77</v>
       </c>
       <c r="G14" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="H14" t="b">
         <v>0</v>
       </c>
       <c r="I14" s="3" t="inlineStr"/>
       <c r="J14" s="2" t="n">
-        <v>0.3634349030470914</v>
+        <v>0.4892787524366471</v>
       </c>
       <c r="K14" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="L14" t="n">
         <v>2</v>
@@ -8472,24 +9477,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>103</v>
+        <v>17</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -8499,10 +9504,10 @@
       </c>
       <c r="I15" s="3" t="inlineStr"/>
       <c r="J15" s="2" t="n">
-        <v>0.3960755813953488</v>
+        <v>0.4719101123595505</v>
       </c>
       <c r="K15" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="L15" t="n">
         <v>2</v>
@@ -8529,27 +9534,27 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>30</v>
+        <v>-52</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>27</v>
+        <v>317</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="H16" t="b">
         <v>0</v>
       </c>
       <c r="I16" s="3" t="inlineStr"/>
       <c r="J16" s="2" t="n">
-        <v>0.4206896551724138</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>2</v>
@@ -8576,27 +9581,27 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>9</v>
+        <v>-36</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>93</v>
+        <v>141</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H17" t="b">
         <v>0</v>
       </c>
       <c r="I17" s="3" t="inlineStr"/>
       <c r="J17" s="2" t="n">
-        <v>0.8770491803278688</v>
+        <v>0.3632834165280089</v>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="L17" t="n">
         <v>2</v>
@@ -8623,27 +9628,27 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>-21</v>
+        <v>39</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="G18" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H18" t="b">
         <v>0</v>
       </c>
       <c r="I18" s="3" t="inlineStr"/>
       <c r="J18" s="2" t="n">
-        <v>0.52046783625731</v>
+        <v>0.3960755813953488</v>
       </c>
       <c r="K18" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="L18" t="n">
         <v>2</v>
@@ -8670,14 +9675,14 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -8687,7 +9692,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr"/>
       <c r="J19" s="2" t="n">
-        <v>0.4772727272727273</v>
+        <v>0.4178082191780822</v>
       </c>
       <c r="K19" t="n">
         <v>2</v>
@@ -8696,6 +9701,147 @@
         <v>2</v>
       </c>
       <c r="M19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>93</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3" t="inlineStr"/>
+      <c r="J20" s="2" t="n">
+        <v>0.8492063492063492</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>-21</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>77</v>
+      </c>
+      <c r="G21" t="n">
+        <v>21</v>
+      </c>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3" t="inlineStr"/>
+      <c r="J21" s="2" t="n">
+        <v>0.52046783625731</v>
+      </c>
+      <c r="K21" t="n">
+        <v>5</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3" t="inlineStr"/>
+      <c r="J22" s="2" t="n">
+        <v>0.4719101123595505</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" t="b">
         <v>1</v>
       </c>
     </row>
